--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ez_facture_excel_local\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFA05EB-78C1-4DBB-BFD9-BA3B4460C827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9596A92-B6C8-4203-B087-31F41149457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{73B8519F-31D5-489C-8AD9-62A11CBFF5A8}"/>
   </bookViews>
@@ -23,6 +23,7 @@
     <sheet name="aide" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="AAB" localSheetId="6">config!$B$20</definedName>
     <definedName name="acompte" localSheetId="2">avoir!$I$31</definedName>
     <definedName name="acompte" localSheetId="0">devis!$I$31</definedName>
     <definedName name="acompte" localSheetId="1">facture!$I$31</definedName>
@@ -67,12 +68,12 @@
     <definedName name="fact_date_livraison" localSheetId="1">facture!$I$9</definedName>
     <definedName name="fact_num_fact" localSheetId="1">facture!$I$4</definedName>
     <definedName name="fact_ref_commande" localSheetId="1">facture!$I$6</definedName>
-    <definedName name="first_avoir_number">config!$B$18</definedName>
-    <definedName name="first_invoice_number">config!$B$17</definedName>
-    <definedName name="footer">config!$B$15</definedName>
-    <definedName name="instructions_paiement">config!$B$14</definedName>
+    <definedName name="first_avoir_number">config!$B$17</definedName>
+    <definedName name="first_invoice_number">config!$B$16</definedName>
+    <definedName name="footer">config!$B$14</definedName>
+    <definedName name="instructions_paiement">config!#REF!</definedName>
     <definedName name="liste_cat_taxes">listes!$E$3:$E$19</definedName>
-    <definedName name="liste_regimes_tva">config!$E$17:$E$18</definedName>
+    <definedName name="liste_regimes_tva">config!$E$16:$E$17</definedName>
     <definedName name="logo" localSheetId="2">avoir!$B$4</definedName>
     <definedName name="logo" localSheetId="0">devis!$B$4</definedName>
     <definedName name="logo" localSheetId="1">facture!$B$4</definedName>
@@ -84,6 +85,8 @@
     <definedName name="num_client" localSheetId="2">avoir!$I$7</definedName>
     <definedName name="num_client" localSheetId="0">devis!$I$6</definedName>
     <definedName name="num_client" localSheetId="1">facture!$I$7</definedName>
+    <definedName name="PMD" localSheetId="6">config!$B$18</definedName>
+    <definedName name="PMT" localSheetId="6">config!$B$19</definedName>
     <definedName name="postalzone">devis!$B$9</definedName>
     <definedName name="Produits">table_produits[#All]</definedName>
     <definedName name="RCS" localSheetId="2">avoir!$C$8</definedName>
@@ -93,7 +96,7 @@
     <definedName name="ref_client">table_clients[Numéro client]</definedName>
     <definedName name="ref_produit">table_produits[Référence produit]</definedName>
     <definedName name="reference_facture" localSheetId="2">avoir!$I$6</definedName>
-    <definedName name="regime_tva">config!$B$16</definedName>
+    <definedName name="regime_tva">config!$B$15</definedName>
     <definedName name="seller_address" localSheetId="2">avoir!$B$8</definedName>
     <definedName name="seller_address" localSheetId="6">config!$B$4</definedName>
     <definedName name="seller_address" localSheetId="0">devis!$B$8</definedName>
@@ -191,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="154">
   <si>
     <t>Facture</t>
   </si>
@@ -577,9 +580,6 @@
   </si>
   <si>
     <t>Les zones éditables sont sur fond gris clair</t>
-  </si>
-  <si>
-    <t>Instructions de paiement</t>
   </si>
   <si>
     <t>Régime de TVA</t>
@@ -722,6 +722,15 @@
   </si>
   <si>
     <t>Les avoirs démarrent au numéro :</t>
+  </si>
+  <si>
+    <t>Retard de paiement</t>
+  </si>
+  <si>
+    <t>Indemnité forfaitaire</t>
+  </si>
+  <si>
+    <t>Escompte</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1192,7 @@
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1674,9 +1683,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1685,6 +1691,51 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1694,10 +1745,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1715,47 +1762,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3014,6 +3020,343 @@
         <family val="2"/>
         <scheme val="major"/>
       </font>
+      <numFmt numFmtId="167" formatCode="0.0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F5F7"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F5F7"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$€]#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F5F7"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F5F7"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F5F7"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F5F7"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F5F7"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5D7079"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$€]#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$€]#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F5F7"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
       <numFmt numFmtId="166" formatCode="0.000"/>
       <fill>
         <patternFill patternType="solid">
@@ -3272,343 +3615,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="[$€]#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="[$€]#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F5F7"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.0%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F5F7"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.0%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F5F7"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="[$€]#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F5F7"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F5F7"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F5F7"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F5F7"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F5F7"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5D7079"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3629,24 +3635,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B437C664-0EAF-4959-84A4-9A65E936C576}" name="lignes_devis" displayName="lignes_devis" ref="B23:I26" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65" tableBorderDxfId="64" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B437C664-0EAF-4959-84A4-9A65E936C576}" name="lignes_devis" displayName="lignes_devis" ref="B23:I26" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54" tableBorderDxfId="53" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F483E378-C725-476E-8EF0-74295A577FC3}" name="Référence" dataDxfId="63" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{49ECA7E0-65BD-44B3-9C24-560CD2B91077}" name="Description" dataDxfId="62" dataCellStyle="Normal 2">
+    <tableColumn id="1" xr3:uid="{F483E378-C725-476E-8EF0-74295A577FC3}" name="Référence" dataDxfId="52" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{49ECA7E0-65BD-44B3-9C24-560CD2B91077}" name="Description" dataDxfId="51" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Description],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4A7FDED9-29BD-4465-B6C9-74ED3A4AC2B3}" name="Quantité" dataDxfId="61" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{4562A9B0-FFB0-423B-94EA-A3FF71334FC8}" name="Prix unitaire HT" dataDxfId="60" dataCellStyle="Normal 2">
+    <tableColumn id="3" xr3:uid="{4A7FDED9-29BD-4465-B6C9-74ED3A4AC2B3}" name="Quantité" dataDxfId="50" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{4562A9B0-FFB0-423B-94EA-A3FF71334FC8}" name="Prix unitaire HT" dataDxfId="49" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{81A2AA13-E5CA-43D7-B956-A4AEE95E02B3}" name="% TVA" dataDxfId="59" dataCellStyle="Pourcentage">
+    <tableColumn id="5" xr3:uid="{81A2AA13-E5CA-43D7-B956-A4AEE95E02B3}" name="% TVA" dataDxfId="48" dataCellStyle="Pourcentage">
       <calculatedColumnFormula>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Taux TVA],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{968DA6D3-0406-4997-AD42-A99CD5AE4CE8}" name="Cat" dataDxfId="58" dataCellStyle="Pourcentage">
+    <tableColumn id="8" xr3:uid="{968DA6D3-0406-4997-AD42-A99CD5AE4CE8}" name="Cat" dataDxfId="47" dataCellStyle="Pourcentage">
       <calculatedColumnFormula>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Cat],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{85ED7750-92BC-4FDD-B984-86A54A74287F}" name="Remise" dataDxfId="57" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{CD2ECC04-FC19-41FC-B6AC-89A90B8A7BF2}" name="Prix total HT" dataDxfId="56" dataCellStyle="Normal 2">
+    <tableColumn id="6" xr3:uid="{85ED7750-92BC-4FDD-B984-86A54A74287F}" name="Remise" dataDxfId="46" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{CD2ECC04-FC19-41FC-B6AC-89A90B8A7BF2}" name="Prix total HT" dataDxfId="45" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(B24="",0,lignes_devis[[#This Row],[Quantité]]*lignes_devis[[#This Row],[Prix unitaire HT]]-lignes_devis[[#This Row],[Remise]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3655,7 +3661,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4048CC68-0954-4561-A5C2-FBF0AC221B28}" name="lignes_facture" displayName="lignes_facture" ref="B23:I26" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54" tableBorderDxfId="53" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4048CC68-0954-4561-A5C2-FBF0AC221B28}" name="lignes_facture" displayName="lignes_facture" ref="B23:I26" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65" tableBorderDxfId="64" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B23:I26" xr:uid="{4048CC68-0954-4561-A5C2-FBF0AC221B28}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3667,22 +3673,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{93A1E92A-3269-4930-9F2D-27BA834EF3EA}" name="Référence" dataDxfId="52" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{782EF3A3-363D-49FB-B672-3FC7BD4089CF}" name="Description" dataDxfId="51" dataCellStyle="Normal 2">
+    <tableColumn id="1" xr3:uid="{93A1E92A-3269-4930-9F2D-27BA834EF3EA}" name="Référence" dataDxfId="63" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{782EF3A3-363D-49FB-B672-3FC7BD4089CF}" name="Description" dataDxfId="62" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Description],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5B35AF0A-2EC3-4E68-B0DE-5196DA81226F}" name="Quantité" dataDxfId="50" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{14C7271B-481E-4F7F-B344-E8B60C4B6EFB}" name="Prix unitaire HT" dataDxfId="49" dataCellStyle="Normal 2">
+    <tableColumn id="3" xr3:uid="{5B35AF0A-2EC3-4E68-B0DE-5196DA81226F}" name="Quantité" dataDxfId="61" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{14C7271B-481E-4F7F-B344-E8B60C4B6EFB}" name="Prix unitaire HT" dataDxfId="60" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FB45F800-8089-4025-935C-AB20DD9E25A8}" name="% TVA" dataDxfId="48" dataCellStyle="Normal 2">
+    <tableColumn id="5" xr3:uid="{FB45F800-8089-4025-935C-AB20DD9E25A8}" name="% TVA" dataDxfId="59" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Taux TVA],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8C01E363-89C6-45D4-AF39-41B46F2F8BE2}" name="Cat" dataDxfId="47" dataCellStyle="Normal 2">
+    <tableColumn id="8" xr3:uid="{8C01E363-89C6-45D4-AF39-41B46F2F8BE2}" name="Cat" dataDxfId="58" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Cat],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6CA4A53A-8738-4E7D-A0D9-9B24C3095CE1}" name="Remise" dataDxfId="46" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{BDD20081-7F9A-4190-959D-B1E1F26F588D}" name="Prix total HT" dataDxfId="45" dataCellStyle="Normal 2">
+    <tableColumn id="6" xr3:uid="{6CA4A53A-8738-4E7D-A0D9-9B24C3095CE1}" name="Remise" dataDxfId="57" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{BDD20081-7F9A-4190-959D-B1E1F26F588D}" name="Prix total HT" dataDxfId="56" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(B24="",0,lignes_facture[[#This Row],[Quantité]]*lignes_facture[[#This Row],[Prix unitaire HT]]-lignes_facture[[#This Row],[Remise]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4159,7 +4165,7 @@
       </c>
       <c r="I7" s="116">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
@@ -4205,11 +4211,11 @@
       </c>
       <c r="C11" s="42"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="177"/>
+      <c r="E11" s="186"/>
+      <c r="F11" s="187"/>
+      <c r="G11" s="187"/>
+      <c r="H11" s="187"/>
+      <c r="I11" s="188"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="89" t="s">
@@ -4217,21 +4223,21 @@
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="177"/>
+      <c r="E12" s="186"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="187"/>
+      <c r="H12" s="187"/>
+      <c r="I12" s="188"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="42"/>
       <c r="C13" s="43"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="179"/>
-      <c r="H13" s="179"/>
-      <c r="I13" s="180"/>
+      <c r="E13" s="189"/>
+      <c r="F13" s="190"/>
+      <c r="G13" s="190"/>
+      <c r="H13" s="190"/>
+      <c r="I13" s="191"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D14" s="5"/>
@@ -4363,7 +4369,7 @@
         <v>17</v>
       </c>
       <c r="G23" s="72" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H23" s="50" t="s">
         <v>23</v>
@@ -4458,11 +4464,11 @@
       <c r="I27" s="43"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="181" t="s">
+      <c r="B28" s="174" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="182"/>
-      <c r="D28" s="183"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="176"/>
       <c r="E28" s="43"/>
       <c r="F28" s="75"/>
       <c r="G28" s="75"/>
@@ -4475,12 +4481,12 @@
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="184" t="e">
+      <c r="B29" s="177" t="e">
         <f>LEFT(regime_tva,FIND("-",regime_tva)-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="185"/>
-      <c r="D29" s="186"/>
+      <c r="C29" s="178"/>
+      <c r="D29" s="179"/>
       <c r="E29" s="43"/>
       <c r="F29" s="75"/>
       <c r="G29" s="75"/>
@@ -4493,12 +4499,12 @@
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="184" t="str">
+      <c r="B30" s="177" t="e">
         <f>IF(ISBLANK(instructions_paiement), "", instructions_paiement)</f>
-        <v/>
-      </c>
-      <c r="C30" s="185"/>
-      <c r="D30" s="186"/>
+        <v>#REF!</v>
+      </c>
+      <c r="C30" s="178"/>
+      <c r="D30" s="179"/>
       <c r="E30" s="43"/>
       <c r="F30" s="75"/>
       <c r="G30" s="75"/>
@@ -4511,9 +4517,9 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="184"/>
-      <c r="C31" s="185"/>
-      <c r="D31" s="186"/>
+      <c r="B31" s="177"/>
+      <c r="C31" s="178"/>
+      <c r="D31" s="179"/>
       <c r="E31" s="43"/>
       <c r="F31" s="75"/>
       <c r="G31" s="75"/>
@@ -4525,9 +4531,9 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="187"/>
-      <c r="C32" s="188"/>
-      <c r="D32" s="189"/>
+      <c r="B32" s="180"/>
+      <c r="C32" s="181"/>
+      <c r="D32" s="182"/>
       <c r="E32" s="43"/>
       <c r="F32" s="75"/>
       <c r="G32" s="75"/>
@@ -4550,16 +4556,16 @@
       <c r="I33" s="12"/>
     </row>
     <row r="34" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="170" t="s">
+      <c r="B34" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="171"/>
-      <c r="D34" s="172"/>
-      <c r="E34" s="172"/>
-      <c r="F34" s="172"/>
-      <c r="G34" s="172"/>
-      <c r="H34" s="172"/>
-      <c r="I34" s="172"/>
+      <c r="C34" s="184"/>
+      <c r="D34" s="185"/>
+      <c r="E34" s="185"/>
+      <c r="F34" s="185"/>
+      <c r="G34" s="185"/>
+      <c r="H34" s="185"/>
+      <c r="I34" s="185"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="24"/>
@@ -4572,37 +4578,37 @@
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="173" t="str">
+      <c r="B36" s="172" t="str">
         <f>IF(ISBLANK(footer), "", footer)</f>
         <v/>
       </c>
-      <c r="C36" s="173"/>
-      <c r="D36" s="174"/>
-      <c r="E36" s="174"/>
-      <c r="F36" s="174"/>
-      <c r="G36" s="174"/>
-      <c r="H36" s="174"/>
-      <c r="I36" s="174"/>
+      <c r="C36" s="172"/>
+      <c r="D36" s="173"/>
+      <c r="E36" s="173"/>
+      <c r="F36" s="173"/>
+      <c r="G36" s="173"/>
+      <c r="H36" s="173"/>
+      <c r="I36" s="173"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="174"/>
-      <c r="C37" s="174"/>
-      <c r="D37" s="174"/>
-      <c r="E37" s="174"/>
-      <c r="F37" s="174"/>
-      <c r="G37" s="174"/>
-      <c r="H37" s="174"/>
-      <c r="I37" s="174"/>
+      <c r="B37" s="173"/>
+      <c r="C37" s="173"/>
+      <c r="D37" s="173"/>
+      <c r="E37" s="173"/>
+      <c r="F37" s="173"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="173"/>
+      <c r="I37" s="173"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="174"/>
-      <c r="C38" s="174"/>
-      <c r="D38" s="174"/>
-      <c r="E38" s="174"/>
-      <c r="F38" s="174"/>
-      <c r="G38" s="174"/>
-      <c r="H38" s="174"/>
-      <c r="I38" s="174"/>
+      <c r="B38" s="173"/>
+      <c r="C38" s="173"/>
+      <c r="D38" s="173"/>
+      <c r="E38" s="173"/>
+      <c r="F38" s="173"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="173"/>
+      <c r="I38" s="173"/>
     </row>
     <row r="39" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="13"/>
@@ -4738,7 +4744,7 @@
       </c>
       <c r="I8" s="113">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -4945,7 +4951,7 @@
         <v>17</v>
       </c>
       <c r="G23" s="72" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H23" s="50" t="s">
         <v>23</v>
@@ -5030,11 +5036,11 @@
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="181" t="s">
+      <c r="B28" s="174" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="182"/>
-      <c r="D28" s="183"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="176"/>
       <c r="F28" s="75"/>
       <c r="G28" s="75"/>
       <c r="H28" s="45" t="s">
@@ -5046,12 +5052,12 @@
       </c>
     </row>
     <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="184" t="e">
+      <c r="B29" s="177" t="e">
         <f>LEFT(regime_tva,FIND("-",regime_tva)-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="185"/>
-      <c r="D29" s="186"/>
+      <c r="C29" s="178"/>
+      <c r="D29" s="179"/>
       <c r="F29" s="75"/>
       <c r="G29" s="75"/>
       <c r="H29" s="45" t="s">
@@ -5063,12 +5069,12 @@
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="184" t="str">
-        <f>IF(ISBLANK(instructions_paiement), "", instructions_paiement)</f>
-        <v/>
-      </c>
-      <c r="C30" s="185"/>
-      <c r="D30" s="186"/>
+      <c r="B30" s="177" t="str">
+        <f>config!PMD&amp;". "&amp;config!PMT&amp;". "&amp;config!AAB&amp;". "</f>
+        <v xml:space="preserve">. . . </v>
+      </c>
+      <c r="C30" s="178"/>
+      <c r="D30" s="179"/>
       <c r="F30" s="75"/>
       <c r="G30" s="75"/>
       <c r="H30" s="45" t="s">
@@ -5080,9 +5086,9 @@
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="184"/>
-      <c r="C31" s="185"/>
-      <c r="D31" s="186"/>
+      <c r="B31" s="177"/>
+      <c r="C31" s="178"/>
+      <c r="D31" s="179"/>
       <c r="F31" s="75"/>
       <c r="G31" s="75"/>
       <c r="H31" s="45" t="s">
@@ -5093,9 +5099,9 @@
       </c>
     </row>
     <row r="32" spans="2:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="187"/>
-      <c r="C32" s="188"/>
-      <c r="D32" s="189"/>
+      <c r="B32" s="180"/>
+      <c r="C32" s="181"/>
+      <c r="D32" s="182"/>
       <c r="F32" s="75"/>
       <c r="G32" s="75"/>
       <c r="H32" s="46" t="s">
@@ -5144,16 +5150,16 @@
       <c r="I36" s="39"/>
     </row>
     <row r="37" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="190" t="s">
+      <c r="B37" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="191"/>
-      <c r="D37" s="192"/>
-      <c r="E37" s="192"/>
-      <c r="F37" s="192"/>
-      <c r="G37" s="192"/>
-      <c r="H37" s="192"/>
-      <c r="I37" s="192"/>
+      <c r="C37" s="170"/>
+      <c r="D37" s="171"/>
+      <c r="E37" s="171"/>
+      <c r="F37" s="171"/>
+      <c r="G37" s="171"/>
+      <c r="H37" s="171"/>
+      <c r="I37" s="171"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="47"/>
@@ -5166,37 +5172,37 @@
       <c r="I38" s="39"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="173" t="str">
+      <c r="B39" s="172" t="str">
         <f>IF(ISBLANK(footer), "", footer)</f>
         <v/>
       </c>
-      <c r="C39" s="173"/>
-      <c r="D39" s="174"/>
-      <c r="E39" s="174"/>
-      <c r="F39" s="174"/>
-      <c r="G39" s="174"/>
-      <c r="H39" s="174"/>
-      <c r="I39" s="174"/>
+      <c r="C39" s="172"/>
+      <c r="D39" s="173"/>
+      <c r="E39" s="173"/>
+      <c r="F39" s="173"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="173"/>
+      <c r="I39" s="173"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="174"/>
-      <c r="C40" s="174"/>
-      <c r="D40" s="174"/>
-      <c r="E40" s="174"/>
-      <c r="F40" s="174"/>
-      <c r="G40" s="174"/>
-      <c r="H40" s="174"/>
-      <c r="I40" s="174"/>
+      <c r="B40" s="173"/>
+      <c r="C40" s="173"/>
+      <c r="D40" s="173"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="173"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="173"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="174"/>
-      <c r="C41" s="174"/>
-      <c r="D41" s="174"/>
-      <c r="E41" s="174"/>
-      <c r="F41" s="174"/>
-      <c r="G41" s="174"/>
-      <c r="H41" s="174"/>
-      <c r="I41" s="174"/>
+      <c r="B41" s="173"/>
+      <c r="C41" s="173"/>
+      <c r="D41" s="173"/>
+      <c r="E41" s="173"/>
+      <c r="F41" s="173"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="173"/>
+      <c r="I41" s="173"/>
     </row>
     <row r="42" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="83"/>
@@ -5332,7 +5338,7 @@
       </c>
       <c r="I8" s="116">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -5521,7 +5527,7 @@
         <v>17</v>
       </c>
       <c r="G23" s="72" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H23" s="50" t="s">
         <v>23</v>
@@ -5606,11 +5612,11 @@
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="181" t="s">
+      <c r="B28" s="174" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="182"/>
-      <c r="D28" s="183"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="176"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="16" t="s">
@@ -5622,12 +5628,12 @@
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="184" t="e">
+      <c r="B29" s="177" t="e">
         <f>LEFT(regime_tva,FIND("-",regime_tva)-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="185"/>
-      <c r="D29" s="186"/>
+      <c r="C29" s="178"/>
+      <c r="D29" s="179"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="16" t="s">
@@ -5639,12 +5645,12 @@
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="184" t="str">
+      <c r="B30" s="177" t="e">
         <f>IF(ISBLANK(instructions_paiement), "", instructions_paiement)</f>
-        <v/>
-      </c>
-      <c r="C30" s="185"/>
-      <c r="D30" s="186"/>
+        <v>#REF!</v>
+      </c>
+      <c r="C30" s="178"/>
+      <c r="D30" s="179"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="16" t="s">
@@ -5656,9 +5662,9 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="184"/>
-      <c r="C31" s="185"/>
-      <c r="D31" s="186"/>
+      <c r="B31" s="177"/>
+      <c r="C31" s="178"/>
+      <c r="D31" s="179"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="45" t="s">
@@ -5669,9 +5675,9 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="187"/>
-      <c r="C32" s="188"/>
-      <c r="D32" s="189"/>
+      <c r="B32" s="180"/>
+      <c r="C32" s="181"/>
+      <c r="D32" s="182"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="17" t="s">
@@ -5719,16 +5725,16 @@
       <c r="I36" s="3"/>
     </row>
     <row r="37" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="193" t="s">
+      <c r="B37" s="192" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="194"/>
-      <c r="D37" s="195"/>
-      <c r="E37" s="195"/>
-      <c r="F37" s="195"/>
-      <c r="G37" s="195"/>
-      <c r="H37" s="195"/>
-      <c r="I37" s="195"/>
+      <c r="C37" s="193"/>
+      <c r="D37" s="194"/>
+      <c r="E37" s="194"/>
+      <c r="F37" s="194"/>
+      <c r="G37" s="194"/>
+      <c r="H37" s="194"/>
+      <c r="I37" s="194"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="24"/>
@@ -5741,37 +5747,37 @@
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="173" t="str">
+      <c r="B39" s="172" t="str">
         <f>IF(ISBLANK(footer), "", footer)</f>
         <v/>
       </c>
-      <c r="C39" s="173"/>
-      <c r="D39" s="174"/>
-      <c r="E39" s="174"/>
-      <c r="F39" s="174"/>
-      <c r="G39" s="174"/>
-      <c r="H39" s="174"/>
-      <c r="I39" s="174"/>
+      <c r="C39" s="172"/>
+      <c r="D39" s="173"/>
+      <c r="E39" s="173"/>
+      <c r="F39" s="173"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="173"/>
+      <c r="I39" s="173"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="174"/>
-      <c r="C40" s="174"/>
-      <c r="D40" s="174"/>
-      <c r="E40" s="174"/>
-      <c r="F40" s="174"/>
-      <c r="G40" s="174"/>
-      <c r="H40" s="174"/>
-      <c r="I40" s="174"/>
+      <c r="B40" s="173"/>
+      <c r="C40" s="173"/>
+      <c r="D40" s="173"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="173"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="173"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="174"/>
-      <c r="C41" s="174"/>
-      <c r="D41" s="174"/>
-      <c r="E41" s="174"/>
-      <c r="F41" s="174"/>
-      <c r="G41" s="174"/>
-      <c r="H41" s="174"/>
-      <c r="I41" s="174"/>
+      <c r="B41" s="173"/>
+      <c r="C41" s="173"/>
+      <c r="D41" s="173"/>
+      <c r="E41" s="173"/>
+      <c r="F41" s="173"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="173"/>
+      <c r="I41" s="173"/>
     </row>
     <row r="42" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="13"/>
@@ -5840,58 +5846,58 @@
   <sheetData>
     <row r="1" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="152" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="153" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="153" t="s">
+      <c r="C1" s="154" t="s">
         <v>131</v>
-      </c>
-      <c r="C1" s="154" t="s">
-        <v>132</v>
       </c>
       <c r="D1" s="154" t="s">
         <v>19</v>
       </c>
       <c r="E1" s="154" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F1" s="154" t="s">
         <v>40</v>
       </c>
       <c r="G1" s="154" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="H1" s="154" t="s">
+      <c r="I1" s="154" t="s">
         <v>135</v>
       </c>
-      <c r="I1" s="154" t="s">
+      <c r="J1" s="154" t="s">
         <v>136</v>
       </c>
-      <c r="J1" s="154" t="s">
+      <c r="K1" s="155" t="s">
         <v>137</v>
       </c>
-      <c r="K1" s="155" t="s">
+      <c r="L1" s="154" t="s">
         <v>138</v>
       </c>
-      <c r="L1" s="154" t="s">
+      <c r="M1" s="154" t="s">
         <v>139</v>
       </c>
-      <c r="M1" s="154" t="s">
+      <c r="N1" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="N1" s="154" t="s">
+      <c r="O1" s="154" t="s">
         <v>141</v>
       </c>
-      <c r="O1" s="154" t="s">
+      <c r="P1" s="155" t="s">
         <v>142</v>
       </c>
-      <c r="P1" s="155" t="s">
+      <c r="Q1" s="154" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="154" t="s">
+      <c r="R1" s="154" t="s">
         <v>144</v>
-      </c>
-      <c r="R1" s="154" t="s">
-        <v>145</v>
       </c>
       <c r="S1" s="156" t="s">
         <v>4</v>
@@ -5900,7 +5906,7 @@
         <v>1</v>
       </c>
       <c r="U1" s="154" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="V1" s="157" t="s">
         <v>25</v>
@@ -5970,10 +5976,10 @@
         <v>34</v>
       </c>
       <c r="F1" s="144" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G1" s="144" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H1" s="33" t="s">
         <v>25</v>
@@ -6018,15 +6024,15 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E2" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="101" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B3" s="102">
         <v>0.2</v>
@@ -6043,7 +6049,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="97" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="98">
         <v>0.1</v>
@@ -6058,7 +6064,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="97" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B5" s="99">
         <v>5.5E-2</v>
@@ -6073,7 +6079,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="97" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B6" s="99">
         <v>2.1000000000000001E-2</v>
@@ -6088,7 +6094,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="97" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B7" s="98">
         <v>0</v>
@@ -6371,7 +6377,7 @@
         <v>108</v>
       </c>
       <c r="B31" s="151" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
         <v>109</v>
@@ -6382,7 +6388,7 @@
         <v>110</v>
       </c>
       <c r="B32" s="151" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
         <v>109</v>
@@ -6474,7 +6480,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC6B0481-078B-4FAE-91BE-C3E297EA04B9}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -6487,7 +6493,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" s="164" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6564,43 +6570,52 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="165"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="125" t="s">
         <v>120</v>
       </c>
-      <c r="B14" s="165"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="D15" s="166"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="167"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="166"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="125" t="s">
-        <v>121</v>
-      </c>
       <c r="D16" s="167"/>
-      <c r="E16" s="168"/>
+      <c r="E16" s="167"/>
       <c r="F16" s="168"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>150</v>
       </c>
-      <c r="D17" s="168"/>
-      <c r="E17" s="168"/>
-      <c r="F17" s="169"/>
+      <c r="D17" s="167"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="168"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="169"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>153</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16" xr:uid="{74C65FDA-3756-4D5D-B4F6-7D4AA2A59364}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15" xr:uid="{74C65FDA-3756-4D5D-B4F6-7D4AA2A59364}">
       <formula1>liste_regimes_tva</formula1>
     </dataValidation>
   </dataValidations>
@@ -6638,12 +6653,12 @@
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="107" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="107" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" s="109"/>
       <c r="E6" s="109"/>

--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9596A92-B6C8-4203-B087-31F41149457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31429BA3-A7BC-4F88-ABF5-B7C94E2B66DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{73B8519F-31D5-489C-8AD9-62A11CBFF5A8}"/>
   </bookViews>
@@ -31,6 +31,7 @@
     <definedName name="adresse_client" localSheetId="0">devis!$B$17:$I$21</definedName>
     <definedName name="adresse_client" localSheetId="1">facture!$B$16:$I$21</definedName>
     <definedName name="av_num_avoir" localSheetId="2">avoir!$I$4</definedName>
+    <definedName name="backup" localSheetId="6">config!$B$21</definedName>
     <definedName name="buyer_address" localSheetId="2">avoir!$B$18</definedName>
     <definedName name="buyer_address" localSheetId="1">facture!$B$18</definedName>
     <definedName name="buyer_city" localSheetId="2">avoir!$B$20</definedName>
@@ -194,7 +195,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="155">
   <si>
     <t>Facture</t>
   </si>
@@ -731,6 +732,9 @@
   </si>
   <si>
     <t>Escompte</t>
+  </si>
+  <si>
+    <t>Répertoire de sauvegarde json</t>
   </si>
 </sst>
 </file>
@@ -4165,7 +4169,7 @@
       </c>
       <c r="I7" s="116">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
@@ -4744,7 +4748,7 @@
       </c>
       <c r="I8" s="113">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -5338,7 +5342,7 @@
       </c>
       <c r="I8" s="116">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -6480,7 +6484,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC6B0481-078B-4FAE-91BE-C3E297EA04B9}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -6611,6 +6615,11 @@
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31429BA3-A7BC-4F88-ABF5-B7C94E2B66DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED53646-0B77-46FC-ADA2-BD6B4A5203C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{73B8519F-31D5-489C-8AD9-62A11CBFF5A8}"/>
   </bookViews>
@@ -57,8 +57,9 @@
     <definedName name="buyer_tax_scheme" localSheetId="6">config!#REF!</definedName>
     <definedName name="buyer_tax_scheme_id" localSheetId="2">avoir!$C$19</definedName>
     <definedName name="buyer_tax_scheme_id" localSheetId="1">facture!$C$19</definedName>
-    <definedName name="date_facture" localSheetId="2">avoir!$I$8</definedName>
+    <definedName name="date_facture" localSheetId="2">avoir!$I$9</definedName>
     <definedName name="date_facture" localSheetId="1">facture!$I$8</definedName>
+    <definedName name="date_facture_reference" localSheetId="2">avoir!$I$7</definedName>
     <definedName name="description_devis" localSheetId="0">devis!$E$11</definedName>
     <definedName name="dev_date_devis" localSheetId="0">devis!$I$7</definedName>
     <definedName name="dev_date_valid" localSheetId="0">devis!$I$8</definedName>
@@ -83,7 +84,7 @@
     <definedName name="net_a_payer" localSheetId="1">facture!$I$32</definedName>
     <definedName name="note_avoir" localSheetId="2">avoir!$B$37</definedName>
     <definedName name="note_facture" localSheetId="1">facture!$B$37</definedName>
-    <definedName name="num_client" localSheetId="2">avoir!$I$7</definedName>
+    <definedName name="num_client" localSheetId="2">avoir!$I$8</definedName>
     <definedName name="num_client" localSheetId="0">devis!$I$6</definedName>
     <definedName name="num_client" localSheetId="1">facture!$I$7</definedName>
     <definedName name="PMD" localSheetId="6">config!$B$18</definedName>
@@ -195,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="156">
   <si>
     <t>Facture</t>
   </si>
@@ -735,6 +736,9 @@
   </si>
   <si>
     <t>Répertoire de sauvegarde json</t>
+  </si>
+  <si>
+    <t>Datée du :</t>
   </si>
 </sst>
 </file>
@@ -963,7 +967,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1066,19 +1070,6 @@
       <bottom style="thin">
         <color theme="0"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1196,7 +1187,7 @@
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1488,7 +1479,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1505,13 +1495,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1566,15 +1556,9 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1591,15 +1575,15 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1631,15 +1615,15 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1648,7 +1632,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1695,6 +1679,32 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1710,6 +1720,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1718,16 +1732,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1737,9 +1750,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1749,12 +1759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1762,9 +1775,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4153,7 +4163,7 @@
       <c r="H6" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="115"/>
+      <c r="I6" s="114"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="91" t="s">
@@ -4167,7 +4177,7 @@
       <c r="H7" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="116">
+      <c r="I7" s="115">
         <f ca="1">TODAY()</f>
         <v>46225</v>
       </c>
@@ -4184,7 +4194,7 @@
       <c r="H8" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="117"/>
+      <c r="I8" s="116"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="89" t="s">
@@ -4201,13 +4211,13 @@
       </c>
       <c r="C10" s="42"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="130" t="s">
+      <c r="E10" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="132"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="127"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="93" t="s">
@@ -4215,11 +4225,11 @@
       </c>
       <c r="C11" s="42"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="186"/>
-      <c r="F11" s="187"/>
-      <c r="G11" s="187"/>
-      <c r="H11" s="187"/>
-      <c r="I11" s="188"/>
+      <c r="E11" s="192"/>
+      <c r="F11" s="193"/>
+      <c r="G11" s="193"/>
+      <c r="H11" s="193"/>
+      <c r="I11" s="194"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="89" t="s">
@@ -4227,21 +4237,21 @@
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="187"/>
-      <c r="G12" s="187"/>
-      <c r="H12" s="187"/>
-      <c r="I12" s="188"/>
+      <c r="E12" s="192"/>
+      <c r="F12" s="193"/>
+      <c r="G12" s="193"/>
+      <c r="H12" s="193"/>
+      <c r="I12" s="194"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="42"/>
       <c r="C13" s="43"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="189"/>
-      <c r="F13" s="190"/>
-      <c r="G13" s="190"/>
-      <c r="H13" s="190"/>
-      <c r="I13" s="191"/>
+      <c r="E13" s="195"/>
+      <c r="F13" s="196"/>
+      <c r="G13" s="196"/>
+      <c r="H13" s="196"/>
+      <c r="I13" s="197"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D14" s="5"/>
@@ -4261,17 +4271,17 @@
       <c r="I15" s="50"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="110"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
+      <c r="B16" s="109"/>
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="109"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="109"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="118" t="str">
+      <c r="B17" s="117" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
       </c>
@@ -4279,15 +4289,15 @@
         <f>IF(num_client="","Téléphone",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Téléphone],""))</f>
         <v>Téléphone</v>
       </c>
-      <c r="D17" s="110"/>
-      <c r="E17" s="119" t="str">
+      <c r="D17" s="109"/>
+      <c r="E17" s="118" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
       </c>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="63" t="str">
@@ -4341,7 +4351,7 @@
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="111" t="str">
+      <c r="B21" s="110" t="str">
         <f>IF(num_client="","Pays",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation Pays],""),""))</f>
         <v>Pays</v>
       </c>
@@ -4393,11 +4403,11 @@
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F24" s="126" t="str">
+      <c r="F24" s="121" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G24" s="126" t="str">
+      <c r="G24" s="121" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
@@ -4418,11 +4428,11 @@
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F25" s="126" t="str">
+      <c r="F25" s="121" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G25" s="126" t="str">
+      <c r="G25" s="121" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
@@ -4443,11 +4453,11 @@
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F26" s="127" t="str">
+      <c r="F26" s="122" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G26" s="127" t="str">
+      <c r="G26" s="122" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
@@ -4468,11 +4478,11 @@
       <c r="I27" s="43"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="174" t="s">
+      <c r="B28" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="175"/>
-      <c r="D28" s="176"/>
+      <c r="C28" s="181"/>
+      <c r="D28" s="182"/>
       <c r="E28" s="43"/>
       <c r="F28" s="75"/>
       <c r="G28" s="75"/>
@@ -4485,12 +4495,12 @@
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="177" t="e">
+      <c r="B29" s="183" t="e">
         <f>LEFT(regime_tva,FIND("-",regime_tva)-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="178"/>
-      <c r="D29" s="179"/>
+      <c r="C29" s="184"/>
+      <c r="D29" s="185"/>
       <c r="E29" s="43"/>
       <c r="F29" s="75"/>
       <c r="G29" s="75"/>
@@ -4503,12 +4513,12 @@
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="177" t="e">
-        <f>IF(ISBLANK(instructions_paiement), "", instructions_paiement)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C30" s="178"/>
-      <c r="D30" s="179"/>
+      <c r="B30" s="183" t="str">
+        <f>config!PMD&amp;". "&amp;config!PMT&amp;". "&amp;config!AAB&amp;". "</f>
+        <v xml:space="preserve">. . . </v>
+      </c>
+      <c r="C30" s="184"/>
+      <c r="D30" s="185"/>
       <c r="E30" s="43"/>
       <c r="F30" s="75"/>
       <c r="G30" s="75"/>
@@ -4521,23 +4531,23 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="177"/>
-      <c r="C31" s="178"/>
-      <c r="D31" s="179"/>
+      <c r="B31" s="183"/>
+      <c r="C31" s="184"/>
+      <c r="D31" s="185"/>
       <c r="E31" s="43"/>
       <c r="F31" s="75"/>
       <c r="G31" s="75"/>
       <c r="H31" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="I31" s="129">
+      <c r="I31" s="124">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="180"/>
-      <c r="C32" s="181"/>
-      <c r="D32" s="182"/>
+      <c r="B32" s="186"/>
+      <c r="C32" s="187"/>
+      <c r="D32" s="188"/>
       <c r="E32" s="43"/>
       <c r="F32" s="75"/>
       <c r="G32" s="75"/>
@@ -4560,16 +4570,16 @@
       <c r="I33" s="12"/>
     </row>
     <row r="34" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="183" t="s">
+      <c r="B34" s="189" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="184"/>
-      <c r="D34" s="185"/>
-      <c r="E34" s="185"/>
-      <c r="F34" s="185"/>
-      <c r="G34" s="185"/>
-      <c r="H34" s="185"/>
-      <c r="I34" s="185"/>
+      <c r="C34" s="190"/>
+      <c r="D34" s="191"/>
+      <c r="E34" s="191"/>
+      <c r="F34" s="191"/>
+      <c r="G34" s="191"/>
+      <c r="H34" s="191"/>
+      <c r="I34" s="191"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="24"/>
@@ -4582,37 +4592,37 @@
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="172" t="str">
+      <c r="B36" s="178" t="str">
         <f>IF(ISBLANK(footer), "", footer)</f>
         <v/>
       </c>
-      <c r="C36" s="172"/>
-      <c r="D36" s="173"/>
-      <c r="E36" s="173"/>
-      <c r="F36" s="173"/>
-      <c r="G36" s="173"/>
-      <c r="H36" s="173"/>
-      <c r="I36" s="173"/>
+      <c r="C36" s="178"/>
+      <c r="D36" s="179"/>
+      <c r="E36" s="179"/>
+      <c r="F36" s="179"/>
+      <c r="G36" s="179"/>
+      <c r="H36" s="179"/>
+      <c r="I36" s="179"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="173"/>
-      <c r="C37" s="173"/>
-      <c r="D37" s="173"/>
-      <c r="E37" s="173"/>
-      <c r="F37" s="173"/>
-      <c r="G37" s="173"/>
-      <c r="H37" s="173"/>
-      <c r="I37" s="173"/>
+      <c r="B37" s="179"/>
+      <c r="C37" s="179"/>
+      <c r="D37" s="179"/>
+      <c r="E37" s="179"/>
+      <c r="F37" s="179"/>
+      <c r="G37" s="179"/>
+      <c r="H37" s="179"/>
+      <c r="I37" s="179"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="173"/>
-      <c r="C38" s="173"/>
-      <c r="D38" s="173"/>
-      <c r="E38" s="173"/>
-      <c r="F38" s="173"/>
-      <c r="G38" s="173"/>
-      <c r="H38" s="173"/>
-      <c r="I38" s="173"/>
+      <c r="B38" s="179"/>
+      <c r="C38" s="179"/>
+      <c r="D38" s="179"/>
+      <c r="E38" s="179"/>
+      <c r="F38" s="179"/>
+      <c r="G38" s="179"/>
+      <c r="H38" s="179"/>
+      <c r="I38" s="179"/>
     </row>
     <row r="39" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="13"/>
@@ -4718,7 +4728,7 @@
       <c r="H6" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="112"/>
+      <c r="I6" s="172"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="91" t="s">
@@ -4732,7 +4742,7 @@
       <c r="H7" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="112"/>
+      <c r="I7" s="111"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="89" t="s">
@@ -4746,7 +4756,7 @@
       <c r="H8" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="113">
+      <c r="I8" s="112">
         <f ca="1">TODAY()</f>
         <v>46225</v>
       </c>
@@ -4760,7 +4770,7 @@
       <c r="H9" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="114"/>
+      <c r="I9" s="113"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="89" t="s">
@@ -4772,7 +4782,7 @@
       <c r="H10" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="114"/>
+      <c r="I10" s="113"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="93" t="s">
@@ -4823,16 +4833,16 @@
       <c r="I15" s="39"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="120" t="str">
+      <c r="B16" s="164" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
       </c>
-      <c r="C16" s="63" t="str">
+      <c r="C16" s="165" t="str">
         <f>IF(num_client="","Nom Prénom",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Nom],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Prénom],"")))</f>
         <v>Nom Prénom</v>
       </c>
       <c r="D16" s="39"/>
-      <c r="E16" s="119" t="str">
+      <c r="E16" s="118" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
       </c>
@@ -4842,11 +4852,11 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="63" t="str">
+      <c r="B17" s="165" t="str">
         <f>IF(num_client="","Nom commercial",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Nom commercial],""))</f>
         <v>Nom commercial</v>
       </c>
-      <c r="C17" s="64" t="str">
+      <c r="C17" s="166" t="str">
         <f>IF(num_client="","Téléphone",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Téléphone],""))</f>
         <v>Téléphone</v>
       </c>
@@ -4861,11 +4871,11 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="64" t="str">
+      <c r="B18" s="166" t="str">
         <f>IF(num_client="","Adresse",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation adresse 1],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation adresse 2],"")))</f>
         <v>Adresse</v>
       </c>
-      <c r="C18" s="65" t="str">
+      <c r="C18" s="169" t="str">
         <f>IF(num_client="","Email",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Email],""),""))</f>
         <v>Email</v>
       </c>
@@ -4880,11 +4890,11 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="64" t="str">
+      <c r="B19" s="166" t="str">
         <f>IF(num_client="","CP",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation CP],""),""))</f>
         <v>CP</v>
       </c>
-      <c r="C19" s="120" t="str">
+      <c r="C19" s="164" t="str">
         <f>IF(num_client="","TVA",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[TVA],""))</f>
         <v>TVA</v>
       </c>
@@ -4899,12 +4909,12 @@
       <c r="I19" s="39"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="123" t="str">
+      <c r="B20" s="167" t="str">
         <f>IF(num_client="","Ville",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation Ville],""),""))</f>
         <v>Ville</v>
       </c>
-      <c r="C20" s="121" t="str">
-        <f>IF(num_client="","Siret",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[SIRET],""))</f>
+      <c r="C20" s="170" t="str">
+        <f>IF(num_client="","Siret",TEXT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[SIRET],""),"0"))</f>
         <v>Siret</v>
       </c>
       <c r="D20" s="39"/>
@@ -4918,7 +4928,7 @@
       <c r="I20" s="39"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="124" t="str">
+      <c r="B21" s="168" t="str">
         <f>IF(num_client="","Pays",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation Pays],""),""))</f>
         <v>Pays</v>
       </c>
@@ -4931,7 +4941,7 @@
       <c r="I21" s="39"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="122"/>
+      <c r="B22" s="119"/>
       <c r="D22" s="39"/>
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
@@ -4975,11 +4985,11 @@
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F24" s="105" t="str">
+      <c r="F24" s="104" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G24" s="105" t="str">
+      <c r="G24" s="104" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
@@ -5000,11 +5010,11 @@
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F25" s="105" t="str">
+      <c r="F25" s="104" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G25" s="105" t="str">
+      <c r="G25" s="104" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
@@ -5025,11 +5035,11 @@
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F26" s="106" t="str">
+      <c r="F26" s="105" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G26" s="106" t="str">
+      <c r="G26" s="105" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
@@ -5040,11 +5050,11 @@
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="174" t="s">
+      <c r="B28" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="175"/>
-      <c r="D28" s="176"/>
+      <c r="C28" s="181"/>
+      <c r="D28" s="182"/>
       <c r="F28" s="75"/>
       <c r="G28" s="75"/>
       <c r="H28" s="45" t="s">
@@ -5056,12 +5066,12 @@
       </c>
     </row>
     <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="177" t="e">
+      <c r="B29" s="183" t="e">
         <f>LEFT(regime_tva,FIND("-",regime_tva)-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="178"/>
-      <c r="D29" s="179"/>
+      <c r="C29" s="184"/>
+      <c r="D29" s="185"/>
       <c r="F29" s="75"/>
       <c r="G29" s="75"/>
       <c r="H29" s="45" t="s">
@@ -5073,12 +5083,12 @@
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="177" t="str">
+      <c r="B30" s="183" t="str">
         <f>config!PMD&amp;". "&amp;config!PMT&amp;". "&amp;config!AAB&amp;". "</f>
         <v xml:space="preserve">. . . </v>
       </c>
-      <c r="C30" s="178"/>
-      <c r="D30" s="179"/>
+      <c r="C30" s="184"/>
+      <c r="D30" s="185"/>
       <c r="F30" s="75"/>
       <c r="G30" s="75"/>
       <c r="H30" s="45" t="s">
@@ -5090,9 +5100,9 @@
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="177"/>
-      <c r="C31" s="178"/>
-      <c r="D31" s="179"/>
+      <c r="B31" s="183"/>
+      <c r="C31" s="184"/>
+      <c r="D31" s="185"/>
       <c r="F31" s="75"/>
       <c r="G31" s="75"/>
       <c r="H31" s="45" t="s">
@@ -5103,9 +5113,9 @@
       </c>
     </row>
     <row r="32" spans="2:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="180"/>
-      <c r="C32" s="181"/>
-      <c r="D32" s="182"/>
+      <c r="B32" s="186"/>
+      <c r="C32" s="187"/>
+      <c r="D32" s="188"/>
       <c r="F32" s="75"/>
       <c r="G32" s="75"/>
       <c r="H32" s="46" t="s">
@@ -5117,7 +5127,7 @@
       </c>
       <c r="L32" s="87"/>
     </row>
-    <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="53" t="s">
         <v>27</v>
       </c>
@@ -5129,7 +5139,7 @@
       <c r="H34" s="51"/>
       <c r="I34" s="56"/>
     </row>
-    <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="57" t="s">
         <v>36</v>
       </c>
@@ -5154,16 +5164,16 @@
       <c r="I36" s="39"/>
     </row>
     <row r="37" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="169" t="s">
+      <c r="B37" s="175" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="170"/>
-      <c r="D37" s="171"/>
-      <c r="E37" s="171"/>
-      <c r="F37" s="171"/>
-      <c r="G37" s="171"/>
-      <c r="H37" s="171"/>
-      <c r="I37" s="171"/>
+      <c r="C37" s="176"/>
+      <c r="D37" s="177"/>
+      <c r="E37" s="177"/>
+      <c r="F37" s="177"/>
+      <c r="G37" s="177"/>
+      <c r="H37" s="177"/>
+      <c r="I37" s="177"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="47"/>
@@ -5176,37 +5186,37 @@
       <c r="I38" s="39"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="172" t="str">
+      <c r="B39" s="178" t="str">
         <f>IF(ISBLANK(footer), "", footer)</f>
         <v/>
       </c>
-      <c r="C39" s="172"/>
-      <c r="D39" s="173"/>
-      <c r="E39" s="173"/>
-      <c r="F39" s="173"/>
-      <c r="G39" s="173"/>
-      <c r="H39" s="173"/>
-      <c r="I39" s="173"/>
+      <c r="C39" s="178"/>
+      <c r="D39" s="179"/>
+      <c r="E39" s="179"/>
+      <c r="F39" s="179"/>
+      <c r="G39" s="179"/>
+      <c r="H39" s="179"/>
+      <c r="I39" s="179"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="173"/>
-      <c r="C40" s="173"/>
-      <c r="D40" s="173"/>
-      <c r="E40" s="173"/>
-      <c r="F40" s="173"/>
-      <c r="G40" s="173"/>
-      <c r="H40" s="173"/>
-      <c r="I40" s="173"/>
+      <c r="B40" s="179"/>
+      <c r="C40" s="179"/>
+      <c r="D40" s="179"/>
+      <c r="E40" s="179"/>
+      <c r="F40" s="179"/>
+      <c r="G40" s="179"/>
+      <c r="H40" s="179"/>
+      <c r="I40" s="179"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="173"/>
-      <c r="C41" s="173"/>
-      <c r="D41" s="173"/>
-      <c r="E41" s="173"/>
-      <c r="F41" s="173"/>
-      <c r="G41" s="173"/>
-      <c r="H41" s="173"/>
-      <c r="I41" s="173"/>
+      <c r="B41" s="179"/>
+      <c r="C41" s="179"/>
+      <c r="D41" s="179"/>
+      <c r="E41" s="179"/>
+      <c r="F41" s="179"/>
+      <c r="G41" s="179"/>
+      <c r="H41" s="179"/>
+      <c r="I41" s="179"/>
     </row>
     <row r="42" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="83"/>
@@ -5250,7 +5260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEFA5FEC-6A62-487A-B625-F70127CA37AE}">
-  <dimension ref="B1:I44"/>
+  <dimension ref="B1:K44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="4" customWidth="1"/>
@@ -5266,8 +5276,8 @@
     <col min="11" max="16384" width="11.42578125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -5277,8 +5287,8 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
     </row>
-    <row r="3" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:9" s="1" customFormat="1" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:11" s="1" customFormat="1" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="8"/>
@@ -5289,7 +5299,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="9"/>
     </row>
-    <row r="5" spans="2:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="8"/>
@@ -5299,7 +5309,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="2:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="90" t="s">
         <v>39</v>
       </c>
@@ -5312,9 +5322,10 @@
       <c r="H6" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="115"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I6" s="171"/>
+      <c r="K6" s="174"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="91" t="s">
         <v>40</v>
       </c>
@@ -5324,11 +5335,11 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="115"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="I7" s="173"/>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="89" t="s">
         <v>43</v>
       </c>
@@ -5338,24 +5349,26 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="116">
-        <f ca="1">TODAY()</f>
-        <v>46225</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="I8" s="114"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="89" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="43"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="94"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H9" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="115">
+        <f ca="1">TODAY()</f>
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="89" t="s">
         <v>22</v>
       </c>
@@ -5365,7 +5378,7 @@
       <c r="H10" s="20"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="93" t="s">
         <v>4</v>
       </c>
@@ -5377,7 +5390,7 @@
       <c r="H11" s="5"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="89" t="s">
         <v>1</v>
       </c>
@@ -5389,7 +5402,7 @@
       <c r="H12" s="5"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -5399,7 +5412,7 @@
       <c r="H13" s="5"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="50" t="s">
         <v>47</v>
       </c>
@@ -5411,7 +5424,7 @@
       <c r="H14" s="50"/>
       <c r="I14" s="50"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="3"/>
@@ -5421,7 +5434,7 @@
       <c r="H15" s="5"/>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="65" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
@@ -5491,7 +5504,7 @@
         <v>Ville</v>
       </c>
       <c r="C20" s="65" t="str">
-        <f>IF(num_client="","Siret",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[SIRET],""))</f>
+        <f>IF(num_client="","Siret",TEXT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[SIRET],""),"0"))</f>
         <v>Siret</v>
       </c>
       <c r="D20" s="39"/>
@@ -5616,11 +5629,11 @@
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="174" t="s">
+      <c r="B28" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="175"/>
-      <c r="D28" s="176"/>
+      <c r="C28" s="181"/>
+      <c r="D28" s="182"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="16" t="s">
@@ -5632,12 +5645,12 @@
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="177" t="e">
+      <c r="B29" s="183" t="e">
         <f>LEFT(regime_tva,FIND("-",regime_tva)-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="178"/>
-      <c r="D29" s="179"/>
+      <c r="C29" s="184"/>
+      <c r="D29" s="185"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="16" t="s">
@@ -5649,12 +5662,12 @@
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="177" t="e">
-        <f>IF(ISBLANK(instructions_paiement), "", instructions_paiement)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C30" s="178"/>
-      <c r="D30" s="179"/>
+      <c r="B30" s="183" t="str">
+        <f>config!PMD&amp;". "&amp;config!PMT&amp;". "&amp;config!AAB&amp;". "</f>
+        <v xml:space="preserve">. . . </v>
+      </c>
+      <c r="C30" s="184"/>
+      <c r="D30" s="185"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="16" t="s">
@@ -5666,22 +5679,22 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="177"/>
-      <c r="C31" s="178"/>
-      <c r="D31" s="179"/>
+      <c r="B31" s="183"/>
+      <c r="C31" s="184"/>
+      <c r="D31" s="185"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="I31" s="128">
+      <c r="I31" s="123">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="180"/>
-      <c r="C32" s="181"/>
-      <c r="D32" s="182"/>
+      <c r="B32" s="186"/>
+      <c r="C32" s="187"/>
+      <c r="D32" s="188"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="17" t="s">
@@ -5692,31 +5705,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="133" t="s">
+    <row r="34" spans="2:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="134"/>
-      <c r="D34" s="135"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="137"/>
-      <c r="G34" s="137"/>
-      <c r="H34" s="134"/>
-      <c r="I34" s="138"/>
-    </row>
-    <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="139" t="s">
+      <c r="C34" s="129"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="132"/>
+      <c r="G34" s="132"/>
+      <c r="H34" s="129"/>
+      <c r="I34" s="133"/>
+    </row>
+    <row r="35" spans="2:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="140"/>
-      <c r="D35" s="135"/>
-      <c r="E35" s="135"/>
-      <c r="F35" s="135"/>
-      <c r="G35" s="135"/>
-      <c r="H35" s="141" t="s">
+      <c r="C35" s="135"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="130"/>
+      <c r="H35" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="I35" s="142"/>
+      <c r="I35" s="137"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="24"/>
@@ -5729,16 +5742,16 @@
       <c r="I36" s="3"/>
     </row>
     <row r="37" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="192" t="s">
+      <c r="B37" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="193"/>
-      <c r="D37" s="194"/>
-      <c r="E37" s="194"/>
-      <c r="F37" s="194"/>
-      <c r="G37" s="194"/>
-      <c r="H37" s="194"/>
-      <c r="I37" s="194"/>
+      <c r="C37" s="199"/>
+      <c r="D37" s="200"/>
+      <c r="E37" s="200"/>
+      <c r="F37" s="200"/>
+      <c r="G37" s="200"/>
+      <c r="H37" s="200"/>
+      <c r="I37" s="200"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="24"/>
@@ -5751,37 +5764,37 @@
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="172" t="str">
+      <c r="B39" s="178" t="str">
         <f>IF(ISBLANK(footer), "", footer)</f>
         <v/>
       </c>
-      <c r="C39" s="172"/>
-      <c r="D39" s="173"/>
-      <c r="E39" s="173"/>
-      <c r="F39" s="173"/>
-      <c r="G39" s="173"/>
-      <c r="H39" s="173"/>
-      <c r="I39" s="173"/>
+      <c r="C39" s="178"/>
+      <c r="D39" s="179"/>
+      <c r="E39" s="179"/>
+      <c r="F39" s="179"/>
+      <c r="G39" s="179"/>
+      <c r="H39" s="179"/>
+      <c r="I39" s="179"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="173"/>
-      <c r="C40" s="173"/>
-      <c r="D40" s="173"/>
-      <c r="E40" s="173"/>
-      <c r="F40" s="173"/>
-      <c r="G40" s="173"/>
-      <c r="H40" s="173"/>
-      <c r="I40" s="173"/>
+      <c r="B40" s="179"/>
+      <c r="C40" s="179"/>
+      <c r="D40" s="179"/>
+      <c r="E40" s="179"/>
+      <c r="F40" s="179"/>
+      <c r="G40" s="179"/>
+      <c r="H40" s="179"/>
+      <c r="I40" s="179"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="173"/>
-      <c r="C41" s="173"/>
-      <c r="D41" s="173"/>
-      <c r="E41" s="173"/>
-      <c r="F41" s="173"/>
-      <c r="G41" s="173"/>
-      <c r="H41" s="173"/>
-      <c r="I41" s="173"/>
+      <c r="B41" s="179"/>
+      <c r="C41" s="179"/>
+      <c r="D41" s="179"/>
+      <c r="E41" s="179"/>
+      <c r="F41" s="179"/>
+      <c r="G41" s="179"/>
+      <c r="H41" s="179"/>
+      <c r="I41" s="179"/>
     </row>
     <row r="42" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="13"/>
@@ -5806,7 +5819,7 @@
     <mergeCell ref="B30:D32"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7" xr:uid="{20F82377-EA80-476D-91E5-E8297DF942F7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" xr:uid="{20F82377-EA80-476D-91E5-E8297DF942F7}">
       <formula1>ref_client</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24:B26" xr:uid="{05F9AAD3-5F57-43DE-9641-8B569CD953E3}">
@@ -5849,96 +5862,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="147" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="153" t="s">
+      <c r="B1" s="148" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="154" t="s">
+      <c r="C1" s="149" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="154" t="s">
+      <c r="D1" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="154" t="s">
+      <c r="E1" s="149" t="s">
         <v>132</v>
       </c>
-      <c r="F1" s="154" t="s">
+      <c r="F1" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="154" t="s">
+      <c r="G1" s="149" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="154" t="s">
+      <c r="H1" s="149" t="s">
         <v>134</v>
       </c>
-      <c r="I1" s="154" t="s">
+      <c r="I1" s="149" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="154" t="s">
+      <c r="J1" s="149" t="s">
         <v>136</v>
       </c>
-      <c r="K1" s="155" t="s">
+      <c r="K1" s="150" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="154" t="s">
+      <c r="L1" s="149" t="s">
         <v>138</v>
       </c>
-      <c r="M1" s="154" t="s">
+      <c r="M1" s="149" t="s">
         <v>139</v>
       </c>
-      <c r="N1" s="154" t="s">
+      <c r="N1" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="O1" s="154" t="s">
+      <c r="O1" s="149" t="s">
         <v>141</v>
       </c>
-      <c r="P1" s="155" t="s">
+      <c r="P1" s="150" t="s">
         <v>142</v>
       </c>
-      <c r="Q1" s="154" t="s">
+      <c r="Q1" s="149" t="s">
         <v>143</v>
       </c>
-      <c r="R1" s="154" t="s">
+      <c r="R1" s="149" t="s">
         <v>144</v>
       </c>
-      <c r="S1" s="156" t="s">
+      <c r="S1" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="154" t="s">
+      <c r="T1" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="154" t="s">
+      <c r="U1" s="149" t="s">
         <v>145</v>
       </c>
-      <c r="V1" s="157" t="s">
+      <c r="V1" s="152" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="21"/>
       <c r="B2" s="22"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
-      <c r="K2" s="159"/>
+      <c r="K2" s="154"/>
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="22"/>
       <c r="O2" s="22"/>
-      <c r="P2" s="159"/>
+      <c r="P2" s="154"/>
       <c r="Q2" s="22"/>
       <c r="R2" s="22"/>
-      <c r="S2" s="160"/>
-      <c r="T2" s="161"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="156"/>
       <c r="U2" s="22"/>
-      <c r="V2" s="162"/>
+      <c r="V2" s="157"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5979,10 +5992,10 @@
       <c r="E1" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="144" t="s">
+      <c r="F1" s="139" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="144" t="s">
+      <c r="G1" s="139" t="s">
         <v>124</v>
       </c>
       <c r="H1" s="33" t="s">
@@ -5995,8 +6008,8 @@
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
       <c r="E2" s="32"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
       <c r="H2" s="34"/>
     </row>
   </sheetData>
@@ -6019,266 +6032,266 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="55" style="95" customWidth="1"/>
+    <col min="2" max="2" width="55" style="94" customWidth="1"/>
     <col min="3" max="3" width="69.42578125" customWidth="1"/>
-    <col min="4" max="4" width="64.85546875" style="100" customWidth="1"/>
-    <col min="5" max="5" width="54.7109375" style="100" customWidth="1"/>
+    <col min="4" max="4" width="64.85546875" style="99" customWidth="1"/>
+    <col min="5" max="5" width="54.7109375" style="99" customWidth="1"/>
     <col min="6" max="6" width="78.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="94" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="E2" s="99" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="102">
+      <c r="B3" s="101">
         <v>0.2</v>
       </c>
-      <c r="C3" s="103" t="s">
+      <c r="C3" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="101" t="s">
+      <c r="D3" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="101" t="s">
+      <c r="E3" s="100" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="96" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="97">
         <v>0.1</v>
       </c>
-      <c r="C4" s="96" t="s">
+      <c r="C4" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97" t="s">
+      <c r="D4" s="96"/>
+      <c r="E4" s="96" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="96" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="99">
+      <c r="B5" s="98">
         <v>5.5E-2</v>
       </c>
-      <c r="C5" s="96" t="s">
+      <c r="C5" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97" t="s">
+      <c r="D5" s="96"/>
+      <c r="E5" s="96" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="96" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="99">
+      <c r="B6" s="98">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97" t="s">
+      <c r="D6" s="96"/>
+      <c r="E6" s="96" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="97" t="s">
+      <c r="A7" s="96" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="98">
+      <c r="B7" s="97">
         <v>0</v>
       </c>
-      <c r="C7" s="96" t="s">
+      <c r="C7" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97" t="s">
+      <c r="D7" s="96"/>
+      <c r="E7" s="96" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="100" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="102">
+      <c r="B8" s="101">
         <v>0.2</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="101" t="s">
+      <c r="D8" s="100" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="101" t="s">
+      <c r="E8" s="100" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="97" t="s">
+      <c r="A9" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="98">
+      <c r="B9" s="97">
         <v>0.1</v>
       </c>
-      <c r="C9" s="96" t="s">
+      <c r="C9" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="97"/>
-      <c r="E9" s="97" t="s">
+      <c r="D9" s="96"/>
+      <c r="E9" s="96" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="99">
+      <c r="B10" s="98">
         <v>5.5E-2</v>
       </c>
-      <c r="C10" s="96" t="s">
+      <c r="C10" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97" t="s">
+      <c r="D10" s="96"/>
+      <c r="E10" s="96" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="97" t="s">
+      <c r="A11" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="99">
+      <c r="B11" s="98">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="C11" s="96" t="s">
+      <c r="C11" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97" t="s">
+      <c r="D11" s="96"/>
+      <c r="E11" s="96" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="98">
+      <c r="B12" s="97">
         <v>0</v>
       </c>
-      <c r="C12" s="96" t="s">
+      <c r="C12" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="97"/>
-      <c r="E12" s="97" t="s">
+      <c r="D12" s="96"/>
+      <c r="E12" s="96" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="146" t="s">
+      <c r="A13" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="146" t="s">
+      <c r="B13" s="101"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="141" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="95" t="s">
+      <c r="A14" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="95" t="s">
+      <c r="B14" s="97"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="94" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="95" t="s">
+      <c r="B15" s="97"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="94" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="97"/>
-      <c r="E16" s="95" t="s">
+      <c r="B16" s="97"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="94" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="97"/>
-      <c r="E17" s="95" t="s">
+      <c r="B17" s="97"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="94" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="95" t="s">
+      <c r="A18" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="98"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="95" t="s">
+      <c r="B18" s="97"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="94" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="147" t="s">
+      <c r="A19" s="142" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="148"/>
-      <c r="C19" s="149"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="147" t="s">
+      <c r="B19" s="143"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="142" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="97"/>
-      <c r="B20" s="97"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="97"/>
+      <c r="A20" s="96"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="95" t="s">
+      <c r="A21" s="94" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="104" t="s">
+      <c r="A22" s="103" t="s">
         <v>87</v>
       </c>
       <c r="B22" t="s">
@@ -6289,7 +6302,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="103" t="s">
         <v>90</v>
       </c>
       <c r="B23" t="s">
@@ -6300,7 +6313,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="104" t="s">
+      <c r="A24" s="103" t="s">
         <v>92</v>
       </c>
       <c r="B24" t="s">
@@ -6311,7 +6324,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="104" t="s">
+      <c r="A25" s="103" t="s">
         <v>94</v>
       </c>
       <c r="B25" t="s">
@@ -6322,7 +6335,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="104" t="s">
+      <c r="A26" s="103" t="s">
         <v>97</v>
       </c>
       <c r="B26" t="s">
@@ -6333,7 +6346,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="104" t="s">
+      <c r="A27" s="103" t="s">
         <v>99</v>
       </c>
       <c r="B27" t="s">
@@ -6344,7 +6357,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="104" t="s">
+      <c r="A28" s="103" t="s">
         <v>101</v>
       </c>
       <c r="B28" t="s">
@@ -6355,7 +6368,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="104" t="s">
+      <c r="A29" s="103" t="s">
         <v>104</v>
       </c>
       <c r="B29" t="s">
@@ -6366,7 +6379,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="104" t="s">
+      <c r="A30" s="103" t="s">
         <v>106</v>
       </c>
       <c r="B30" t="s">
@@ -6377,10 +6390,10 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="104" t="s">
+      <c r="A31" s="103" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="151" t="s">
+      <c r="B31" s="146" t="s">
         <v>126</v>
       </c>
       <c r="C31" t="s">
@@ -6388,10 +6401,10 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="104" t="s">
+      <c r="A32" s="103" t="s">
         <v>110</v>
       </c>
-      <c r="B32" s="151" t="s">
+      <c r="B32" s="146" t="s">
         <v>127</v>
       </c>
       <c r="C32" t="s">
@@ -6399,7 +6412,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="104" t="s">
+      <c r="A33" s="103" t="s">
         <v>111</v>
       </c>
       <c r="B33"/>
@@ -6408,7 +6421,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="95" t="s">
+      <c r="A36" s="94" t="s">
         <v>64</v>
       </c>
     </row>
@@ -6416,7 +6429,7 @@
       <c r="A37" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="95" t="s">
+      <c r="B37" s="94" t="s">
         <v>49</v>
       </c>
     </row>
@@ -6424,7 +6437,7 @@
       <c r="A38" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="95" t="s">
+      <c r="B38" s="94" t="s">
         <v>51</v>
       </c>
     </row>
@@ -6432,7 +6445,7 @@
       <c r="A39" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="95" t="s">
+      <c r="B39" s="94" t="s">
         <v>53</v>
       </c>
     </row>
@@ -6440,7 +6453,7 @@
       <c r="A40" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="94" t="s">
         <v>55</v>
       </c>
     </row>
@@ -6448,7 +6461,7 @@
       <c r="A41" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="95" t="s">
+      <c r="B41" s="94" t="s">
         <v>57</v>
       </c>
     </row>
@@ -6456,7 +6469,7 @@
       <c r="A42" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="95" t="s">
+      <c r="B42" s="94" t="s">
         <v>59</v>
       </c>
     </row>
@@ -6464,7 +6477,7 @@
       <c r="A43" t="s">
         <v>60</v>
       </c>
-      <c r="B43" s="95" t="s">
+      <c r="B43" s="94" t="s">
         <v>61</v>
       </c>
     </row>
@@ -6472,7 +6485,7 @@
       <c r="A44" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="95" t="s">
+      <c r="B44" s="94" t="s">
         <v>63</v>
       </c>
     </row>
@@ -6496,7 +6509,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="164" t="s">
+      <c r="B1" s="159" t="s">
         <v>147</v>
       </c>
     </row>
@@ -6504,103 +6517,103 @@
       <c r="A2" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="143"/>
+      <c r="B2" s="138"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="143"/>
+      <c r="B3" s="138"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="163"/>
+      <c r="B4" s="158"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="143"/>
+      <c r="B5" s="138"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="143"/>
+      <c r="B6" s="138"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="143"/>
+      <c r="B7" s="138"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="143"/>
+      <c r="B8" s="138"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="143"/>
+      <c r="B9" s="138"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="143"/>
+      <c r="B10" s="138"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="143"/>
+      <c r="B11" s="138"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="143"/>
+      <c r="B12" s="138"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="143"/>
+      <c r="B13" s="138"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="165"/>
+      <c r="B14" s="160"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="120" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="166"/>
-      <c r="E15" s="167"/>
-      <c r="F15" s="167"/>
+      <c r="D15" s="161"/>
+      <c r="E15" s="162"/>
+      <c r="F15" s="162"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>149</v>
       </c>
-      <c r="D16" s="167"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="168"/>
+      <c r="D16" s="162"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="163"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>150</v>
       </c>
-      <c r="D17" s="167"/>
-      <c r="E17" s="167"/>
-      <c r="F17" s="168"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="163"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -6638,47 +6651,47 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="94.140625" style="107" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="108" customWidth="1"/>
+    <col min="2" max="2" width="94.140625" style="106" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="107" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" customWidth="1"/>
     <col min="5" max="5" width="5.140625" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="94" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="106" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="95" t="s">
+      <c r="A4" s="94" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="107" t="s">
+      <c r="B5" s="106" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="107" t="s">
+      <c r="B6" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="C6" s="109"/>
-      <c r="E6" s="109"/>
+      <c r="C6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="94" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B9" s="107" t="s">
+      <c r="B9" s="106" t="s">
         <v>117</v>
       </c>
     </row>

--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED53646-0B77-46FC-ADA2-BD6B4A5203C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2955395-4C14-452E-AA47-8248FCEC0B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{73B8519F-31D5-489C-8AD9-62A11CBFF5A8}"/>
   </bookViews>
@@ -82,8 +82,8 @@
     <definedName name="net_a_payer" localSheetId="2">avoir!$I$32</definedName>
     <definedName name="net_a_payer" localSheetId="0">devis!$I$32</definedName>
     <definedName name="net_a_payer" localSheetId="1">facture!$I$32</definedName>
-    <definedName name="note_avoir" localSheetId="2">avoir!$B$37</definedName>
-    <definedName name="note_facture" localSheetId="1">facture!$B$37</definedName>
+    <definedName name="note_avoir" localSheetId="2">avoir!$B$34</definedName>
+    <definedName name="note_facture" localSheetId="1">facture!$B$34</definedName>
     <definedName name="num_client" localSheetId="2">avoir!$I$8</definedName>
     <definedName name="num_client" localSheetId="0">devis!$I$6</definedName>
     <definedName name="num_client" localSheetId="1">facture!$I$7</definedName>
@@ -149,9 +149,9 @@
     <definedName name="total_tva" localSheetId="2">avoir!$I$29</definedName>
     <definedName name="total_tva" localSheetId="0">devis!$I$29</definedName>
     <definedName name="total_tva" localSheetId="1">facture!$I$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">avoir!$A$1:$J$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">avoir!$A$1:$J$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">devis!$A$1:$J$54</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">facture!$A$1:$J$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">facture!$A$1:$J$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="153">
   <si>
     <t>Facture</t>
   </si>
@@ -279,9 +279,6 @@
     <t>Référence</t>
   </si>
   <si>
-    <t>MOYEN DE PAIEMENT :</t>
-  </si>
-  <si>
     <t>Note de facture</t>
   </si>
   <si>
@@ -301,12 +298,6 @@
   </si>
   <si>
     <t>Taux TVA</t>
-  </si>
-  <si>
-    <t>DATE DE PAIEMENT :</t>
-  </si>
-  <si>
-    <t>RÉFÉRENCE DE PAIEMENT :</t>
   </si>
   <si>
     <t>Avoir</t>
@@ -1187,7 +1178,7 @@
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1339,35 +1330,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -1418,9 +1380,6 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1586,26 +1545,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4135,7 +4074,7 @@
       <c r="C4" s="7"/>
       <c r="D4" s="8"/>
       <c r="E4" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
@@ -4152,10 +4091,10 @@
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="90" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="89" t="s">
+      <c r="B6" s="81" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="80" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="5"/>
@@ -4163,42 +4102,42 @@
       <c r="H6" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="114"/>
+      <c r="I6" s="105"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="91" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="89" t="s">
+      <c r="B7" s="82" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="80" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="115">
+        <v>29</v>
+      </c>
+      <c r="I7" s="106">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="89" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="92" t="s">
+      <c r="B8" s="80" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="83" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="116"/>
+        <v>30</v>
+      </c>
+      <c r="I8" s="107"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="89" t="s">
-        <v>42</v>
+      <c r="B9" s="80" t="s">
+        <v>39</v>
       </c>
       <c r="C9" s="43"/>
       <c r="F9" s="5"/>
@@ -4206,52 +4145,52 @@
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="80" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="42"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="125" t="s">
+      <c r="E10" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126"/>
-      <c r="I10" s="127"/>
+      <c r="F10" s="117"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="118"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="84" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="42"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="192"/>
-      <c r="F11" s="193"/>
-      <c r="G11" s="193"/>
-      <c r="H11" s="193"/>
-      <c r="I11" s="194"/>
+      <c r="E11" s="173"/>
+      <c r="F11" s="174"/>
+      <c r="G11" s="174"/>
+      <c r="H11" s="174"/>
+      <c r="I11" s="175"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="89" t="s">
+      <c r="B12" s="80" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="192"/>
-      <c r="F12" s="193"/>
-      <c r="G12" s="193"/>
-      <c r="H12" s="193"/>
-      <c r="I12" s="194"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="174"/>
+      <c r="G12" s="174"/>
+      <c r="H12" s="174"/>
+      <c r="I12" s="175"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="42"/>
       <c r="C13" s="43"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="195"/>
-      <c r="F13" s="196"/>
-      <c r="G13" s="196"/>
-      <c r="H13" s="196"/>
-      <c r="I13" s="197"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="177"/>
+      <c r="G13" s="177"/>
+      <c r="H13" s="177"/>
+      <c r="I13" s="178"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D14" s="5"/>
@@ -4271,45 +4210,45 @@
       <c r="I15" s="50"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="109"/>
-      <c r="C16" s="109"/>
-      <c r="D16" s="109"/>
-      <c r="E16" s="109"/>
-      <c r="F16" s="109"/>
-      <c r="G16" s="109"/>
-      <c r="H16" s="109"/>
-      <c r="I16" s="109"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="117" t="str">
+      <c r="B17" s="108" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
       </c>
-      <c r="C17" s="64" t="str">
+      <c r="C17" s="56" t="str">
         <f>IF(num_client="","Téléphone",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Téléphone],""))</f>
         <v>Téléphone</v>
       </c>
-      <c r="D17" s="109"/>
-      <c r="E17" s="118" t="str">
+      <c r="D17" s="100"/>
+      <c r="E17" s="109" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
       </c>
-      <c r="F17" s="109"/>
-      <c r="G17" s="109"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="63" t="str">
+      <c r="B18" s="55" t="str">
         <f>IF(num_client="","Nom Prénom",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Nom],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Prénom],"")))</f>
         <v>Nom Prénom</v>
       </c>
-      <c r="C18" s="65" t="str">
+      <c r="C18" s="57" t="str">
         <f>IF(num_client="","Email",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Email],""),""))</f>
         <v>Email</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="66" t="str">
+      <c r="E18" s="58" t="str">
         <f>IF(num_client="","Nom Prénom",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Nom],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Prénom],"")))</f>
         <v>Nom Prénom</v>
       </c>
@@ -4319,13 +4258,13 @@
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="64" t="str">
+      <c r="B19" s="56" t="str">
         <f>IF(num_client="","Adresse",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation adresse 1],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation adresse 2],"")))</f>
         <v>Adresse</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="64" t="str">
+      <c r="E19" s="56" t="str">
         <f>IF(num_client="","Adresse",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison adresse 1],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison adresse 2],"")))</f>
         <v>Adresse</v>
       </c>
@@ -4335,13 +4274,13 @@
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="64" t="str">
+      <c r="B20" s="56" t="str">
         <f>IF(num_client="","CP Ville",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation CP],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation Ville],"")))</f>
         <v>CP Ville</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="65" t="str">
+      <c r="E20" s="57" t="str">
         <f>IF(num_client="","CP Ville",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison CP],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison Ville],"")))</f>
         <v>CP Ville</v>
       </c>
@@ -4351,13 +4290,13 @@
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="110" t="str">
+      <c r="B21" s="101" t="str">
         <f>IF(num_client="","Pays",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation Pays],""),""))</f>
         <v>Pays</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="65" t="str">
+      <c r="E21" s="57" t="str">
         <f>IF(num_client="","Pays",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison Pays],""),""))</f>
         <v>Pays</v>
       </c>
@@ -4379,11 +4318,11 @@
       <c r="E23" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="F23" s="72" t="s">
+      <c r="F23" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="72" t="s">
-        <v>122</v>
+      <c r="G23" s="64" t="s">
+        <v>119</v>
       </c>
       <c r="H23" s="50" t="s">
         <v>23</v>
@@ -4393,76 +4332,76 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="61"/>
-      <c r="C24" s="61" t="str">
+      <c r="B24" s="53"/>
+      <c r="C24" s="53" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Description],""))</f>
         <v/>
       </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="62" t="str">
+      <c r="D24" s="53"/>
+      <c r="E24" s="54" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F24" s="121" t="str">
+      <c r="F24" s="112" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G24" s="121" t="str">
+      <c r="G24" s="112" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
-      <c r="H24" s="62"/>
-      <c r="I24" s="88">
+      <c r="H24" s="54"/>
+      <c r="I24" s="79">
         <f>IF(B24="",0,lignes_devis[[#This Row],[Quantité]]*lignes_devis[[#This Row],[Prix unitaire HT]]-lignes_devis[[#This Row],[Remise]])</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="61"/>
-      <c r="C25" s="61" t="str">
+      <c r="B25" s="53"/>
+      <c r="C25" s="53" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Description],""))</f>
         <v/>
       </c>
-      <c r="D25" s="61"/>
-      <c r="E25" s="62" t="str">
+      <c r="D25" s="53"/>
+      <c r="E25" s="54" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F25" s="121" t="str">
+      <c r="F25" s="112" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G25" s="121" t="str">
+      <c r="G25" s="112" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
-      <c r="H25" s="62"/>
-      <c r="I25" s="88">
+      <c r="H25" s="54"/>
+      <c r="I25" s="79">
         <f>IF(B25="",0,lignes_devis[[#This Row],[Quantité]]*lignes_devis[[#This Row],[Prix unitaire HT]]-lignes_devis[[#This Row],[Remise]])</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="61"/>
-      <c r="C26" s="67" t="str">
+      <c r="B26" s="53"/>
+      <c r="C26" s="59" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Description],""))</f>
         <v/>
       </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68" t="str">
+      <c r="D26" s="59"/>
+      <c r="E26" s="60" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F26" s="122" t="str">
+      <c r="F26" s="113" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G26" s="122" t="str">
+      <c r="G26" s="113" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
-      <c r="H26" s="68"/>
-      <c r="I26" s="88">
+      <c r="H26" s="60"/>
+      <c r="I26" s="79">
         <f>IF(B26="",0,lignes_devis[[#This Row],[Quantité]]*lignes_devis[[#This Row],[Prix unitaire HT]]-lignes_devis[[#This Row],[Remise]])</f>
         <v>0</v>
       </c>
@@ -4472,20 +4411,20 @@
       <c r="C27" s="43"/>
       <c r="D27" s="43"/>
       <c r="E27" s="43"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
       <c r="H27" s="43"/>
       <c r="I27" s="43"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="180" t="s">
+      <c r="B28" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="181"/>
-      <c r="D28" s="182"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="163"/>
       <c r="E28" s="43"/>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
       <c r="H28" s="45" t="s">
         <v>15</v>
       </c>
@@ -4495,15 +4434,15 @@
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="183" t="e">
+      <c r="B29" s="164" t="e">
         <f>LEFT(regime_tva,FIND("-",regime_tva)-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="184"/>
-      <c r="D29" s="185"/>
+      <c r="C29" s="165"/>
+      <c r="D29" s="166"/>
       <c r="E29" s="43"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
       <c r="H29" s="45" t="s">
         <v>14</v>
       </c>
@@ -4513,15 +4452,15 @@
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="183" t="str">
+      <c r="B30" s="164" t="str">
         <f>config!PMD&amp;". "&amp;config!PMT&amp;". "&amp;config!AAB&amp;". "</f>
         <v xml:space="preserve">. . . </v>
       </c>
-      <c r="C30" s="184"/>
-      <c r="D30" s="185"/>
+      <c r="C30" s="165"/>
+      <c r="D30" s="166"/>
       <c r="E30" s="43"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
       <c r="H30" s="45" t="s">
         <v>12</v>
       </c>
@@ -4531,26 +4470,26 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="183"/>
-      <c r="C31" s="184"/>
-      <c r="D31" s="185"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="166"/>
       <c r="E31" s="43"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
       <c r="H31" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="I31" s="124">
+      <c r="I31" s="115">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="186"/>
-      <c r="C32" s="187"/>
-      <c r="D32" s="188"/>
+      <c r="B32" s="167"/>
+      <c r="C32" s="168"/>
+      <c r="D32" s="169"/>
       <c r="E32" s="43"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
+      <c r="F32" s="67"/>
+      <c r="G32" s="67"/>
       <c r="H32" s="46" t="s">
         <v>16</v>
       </c>
@@ -4570,16 +4509,16 @@
       <c r="I33" s="12"/>
     </row>
     <row r="34" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="189" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="190"/>
-      <c r="D34" s="191"/>
-      <c r="E34" s="191"/>
-      <c r="F34" s="191"/>
-      <c r="G34" s="191"/>
-      <c r="H34" s="191"/>
-      <c r="I34" s="191"/>
+      <c r="B34" s="170" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="171"/>
+      <c r="D34" s="172"/>
+      <c r="E34" s="172"/>
+      <c r="F34" s="172"/>
+      <c r="G34" s="172"/>
+      <c r="H34" s="172"/>
+      <c r="I34" s="172"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="24"/>
@@ -4592,37 +4531,37 @@
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="178" t="str">
+      <c r="B36" s="159" t="str">
         <f>IF(ISBLANK(footer), "", footer)</f>
         <v/>
       </c>
-      <c r="C36" s="178"/>
-      <c r="D36" s="179"/>
-      <c r="E36" s="179"/>
-      <c r="F36" s="179"/>
-      <c r="G36" s="179"/>
-      <c r="H36" s="179"/>
-      <c r="I36" s="179"/>
+      <c r="C36" s="159"/>
+      <c r="D36" s="160"/>
+      <c r="E36" s="160"/>
+      <c r="F36" s="160"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="160"/>
+      <c r="I36" s="160"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="179"/>
-      <c r="C37" s="179"/>
-      <c r="D37" s="179"/>
-      <c r="E37" s="179"/>
-      <c r="F37" s="179"/>
-      <c r="G37" s="179"/>
-      <c r="H37" s="179"/>
-      <c r="I37" s="179"/>
+      <c r="B37" s="160"/>
+      <c r="C37" s="160"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="160"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="160"/>
+      <c r="I37" s="160"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="179"/>
-      <c r="C38" s="179"/>
-      <c r="D38" s="179"/>
-      <c r="E38" s="179"/>
-      <c r="F38" s="179"/>
-      <c r="G38" s="179"/>
-      <c r="H38" s="179"/>
-      <c r="I38" s="179"/>
+      <c r="B38" s="160"/>
+      <c r="C38" s="160"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="160"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="160"/>
+      <c r="I38" s="160"/>
     </row>
     <row r="39" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="13"/>
@@ -4666,7 +4605,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52097CFB-5AF3-46E2-9BE3-4BF6975CB8DF}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="B1:L44"/>
+  <dimension ref="B1:L41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="43" customWidth="1"/>
@@ -4674,8 +4613,8 @@
     <col min="3" max="3" width="31.140625" style="43" customWidth="1"/>
     <col min="4" max="4" width="10" style="43" customWidth="1"/>
     <col min="5" max="5" width="21.140625" style="43" customWidth="1"/>
-    <col min="6" max="6" width="8" style="71" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" style="71" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="8" style="63" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" style="63" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" style="43" customWidth="1"/>
     <col min="9" max="9" width="18" style="43" customWidth="1"/>
     <col min="10" max="10" width="2.7109375" style="43" customWidth="1"/>
@@ -4684,14 +4623,14 @@
   <sheetData>
     <row r="1" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
     </row>
     <row r="3" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" s="40" customFormat="1" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4701,107 +4640,107 @@
       <c r="E4" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="I4" s="85"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="I4" s="76"/>
     </row>
     <row r="5" spans="2:9" s="40" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
       <c r="D5" s="36"/>
       <c r="E5" s="37"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
       <c r="H5" s="38"/>
-      <c r="I5" s="85"/>
+      <c r="I5" s="76"/>
     </row>
     <row r="6" spans="2:9" s="40" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="90" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="89" t="s">
+      <c r="B6" s="81" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="80" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="36"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="80" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="172"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="153"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="82" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="102"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="111"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="89" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="81" t="s">
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="112">
+      <c r="I8" s="103">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="89" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="81" t="s">
+      <c r="B9" s="80" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="113"/>
+      <c r="I9" s="104"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="80" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="42"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="81" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="113"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="72" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="104"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="84" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="42"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
       <c r="H11" s="44"/>
       <c r="I11" s="41"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="89" t="s">
+      <c r="B12" s="80" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="42"/>
       <c r="E12" s="42"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
       <c r="H12" s="42"/>
       <c r="I12" s="41"/>
     </row>
@@ -4817,8 +4756,8 @@
       <c r="E14" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
       <c r="H14" s="50"/>
       <c r="I14" s="52"/>
     </row>
@@ -4827,124 +4766,124 @@
       <c r="C15" s="42"/>
       <c r="D15" s="39"/>
       <c r="E15" s="42"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
       <c r="H15" s="42"/>
       <c r="I15" s="39"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="164" t="str">
+      <c r="B16" s="145" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
       </c>
-      <c r="C16" s="165" t="str">
+      <c r="C16" s="146" t="str">
         <f>IF(num_client="","Nom Prénom",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Nom],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Prénom],"")))</f>
         <v>Nom Prénom</v>
       </c>
       <c r="D16" s="39"/>
-      <c r="E16" s="118" t="str">
+      <c r="E16" s="109" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
       </c>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
       <c r="H16" s="42"/>
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="165" t="str">
+      <c r="B17" s="146" t="str">
         <f>IF(num_client="","Nom commercial",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Nom commercial],""))</f>
         <v>Nom commercial</v>
       </c>
-      <c r="C17" s="166" t="str">
+      <c r="C17" s="147" t="str">
         <f>IF(num_client="","Téléphone",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Téléphone],""))</f>
         <v>Téléphone</v>
       </c>
       <c r="D17" s="39"/>
-      <c r="E17" s="66" t="str">
+      <c r="E17" s="58" t="str">
         <f>IF(num_client="","Nom Prénom",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Nom],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Prénom],"")))</f>
         <v>Nom Prénom</v>
       </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
       <c r="H17" s="42"/>
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="166" t="str">
+      <c r="B18" s="147" t="str">
         <f>IF(num_client="","Adresse",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation adresse 1],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation adresse 2],"")))</f>
         <v>Adresse</v>
       </c>
-      <c r="C18" s="169" t="str">
+      <c r="C18" s="150" t="str">
         <f>IF(num_client="","Email",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Email],""),""))</f>
         <v>Email</v>
       </c>
       <c r="D18" s="39"/>
-      <c r="E18" s="64" t="str">
+      <c r="E18" s="56" t="str">
         <f>IF(num_client="","Adresse",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison adresse 1],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison adresse 2],"")))</f>
         <v>Adresse</v>
       </c>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
       <c r="H18" s="42"/>
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="166" t="str">
+      <c r="B19" s="147" t="str">
         <f>IF(num_client="","CP",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation CP],""),""))</f>
         <v>CP</v>
       </c>
-      <c r="C19" s="164" t="str">
+      <c r="C19" s="145" t="str">
         <f>IF(num_client="","TVA",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[TVA],""))</f>
         <v>TVA</v>
       </c>
       <c r="D19" s="39"/>
-      <c r="E19" s="65" t="str">
+      <c r="E19" s="57" t="str">
         <f>IF(num_client="","CP Ville",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison CP],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison Ville],"")))</f>
         <v>CP Ville</v>
       </c>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
       <c r="H19" s="42"/>
       <c r="I19" s="39"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="167" t="str">
+      <c r="B20" s="148" t="str">
         <f>IF(num_client="","Ville",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation Ville],""),""))</f>
         <v>Ville</v>
       </c>
-      <c r="C20" s="170" t="str">
+      <c r="C20" s="151" t="str">
         <f>IF(num_client="","Siret",TEXT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[SIRET],""),"0"))</f>
         <v>Siret</v>
       </c>
       <c r="D20" s="39"/>
-      <c r="E20" s="65" t="str">
+      <c r="E20" s="57" t="str">
         <f>IF(num_client="","Pays",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Livraison Pays],""),""))</f>
         <v>Pays</v>
       </c>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
       <c r="H20" s="42"/>
       <c r="I20" s="39"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="168" t="str">
+      <c r="B21" s="149" t="str">
         <f>IF(num_client="","Pays",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation Pays],""),""))</f>
         <v>Pays</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="39"/>
       <c r="E21" s="5"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
       <c r="H21" s="42"/>
       <c r="I21" s="39"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="119"/>
+      <c r="B22" s="110"/>
       <c r="D22" s="39"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
       <c r="H22" s="42"/>
       <c r="I22" s="39"/>
     </row>
@@ -4961,11 +4900,11 @@
       <c r="E23" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="F23" s="72" t="s">
+      <c r="F23" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="72" t="s">
-        <v>122</v>
+      <c r="G23" s="64" t="s">
+        <v>119</v>
       </c>
       <c r="H23" s="50" t="s">
         <v>23</v>
@@ -4975,88 +4914,88 @@
       </c>
     </row>
     <row r="24" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="61"/>
-      <c r="C24" s="61" t="str">
+      <c r="B24" s="53"/>
+      <c r="C24" s="53" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Description],""))</f>
         <v/>
       </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="62" t="str">
+      <c r="D24" s="53"/>
+      <c r="E24" s="54" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F24" s="104" t="str">
+      <c r="F24" s="95" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G24" s="104" t="str">
+      <c r="G24" s="95" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
-      <c r="H24" s="62"/>
-      <c r="I24" s="88">
+      <c r="H24" s="54"/>
+      <c r="I24" s="79">
         <f>IF(B24="",0,lignes_facture[[#This Row],[Quantité]]*lignes_facture[[#This Row],[Prix unitaire HT]]-lignes_facture[[#This Row],[Remise]])</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="61"/>
-      <c r="C25" s="61" t="str">
+      <c r="B25" s="53"/>
+      <c r="C25" s="53" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Description],""))</f>
         <v/>
       </c>
-      <c r="D25" s="61"/>
-      <c r="E25" s="62" t="str">
+      <c r="D25" s="53"/>
+      <c r="E25" s="54" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F25" s="104" t="str">
+      <c r="F25" s="95" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G25" s="104" t="str">
+      <c r="G25" s="95" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
-      <c r="H25" s="62"/>
-      <c r="I25" s="88">
+      <c r="H25" s="54"/>
+      <c r="I25" s="79">
         <f>IF(B25="",0,lignes_facture[[#This Row],[Quantité]]*lignes_facture[[#This Row],[Prix unitaire HT]]-lignes_facture[[#This Row],[Remise]])</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="67"/>
-      <c r="C26" s="67" t="str">
+      <c r="B26" s="59"/>
+      <c r="C26" s="59" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Description],""))</f>
         <v/>
       </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68" t="str">
+      <c r="D26" s="59"/>
+      <c r="E26" s="60" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F26" s="105" t="str">
+      <c r="F26" s="96" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G26" s="105" t="str">
+      <c r="G26" s="96" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
-      <c r="H26" s="68"/>
-      <c r="I26" s="88">
+      <c r="H26" s="60"/>
+      <c r="I26" s="79">
         <f>IF(B26="",0,lignes_facture[[#This Row],[Quantité]]*lignes_facture[[#This Row],[Prix unitaire HT]]-lignes_facture[[#This Row],[Remise]])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="180" t="s">
+      <c r="B28" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="181"/>
-      <c r="D28" s="182"/>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="163"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
       <c r="H28" s="45" t="s">
         <v>15</v>
       </c>
@@ -5066,14 +5005,14 @@
       </c>
     </row>
     <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="183" t="e">
+      <c r="B29" s="164" t="e">
         <f>LEFT(regime_tva,FIND("-",regime_tva)-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="184"/>
-      <c r="D29" s="185"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
+      <c r="C29" s="165"/>
+      <c r="D29" s="166"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
       <c r="H29" s="45" t="s">
         <v>14</v>
       </c>
@@ -5083,14 +5022,14 @@
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="183" t="str">
+      <c r="B30" s="164" t="str">
         <f>config!PMD&amp;". "&amp;config!PMT&amp;". "&amp;config!AAB&amp;". "</f>
         <v xml:space="preserve">. . . </v>
       </c>
-      <c r="C30" s="184"/>
-      <c r="D30" s="185"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
+      <c r="C30" s="165"/>
+      <c r="D30" s="166"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
       <c r="H30" s="45" t="s">
         <v>12</v>
       </c>
@@ -5100,24 +5039,24 @@
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="183"/>
-      <c r="C31" s="184"/>
-      <c r="D31" s="185"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="166"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
       <c r="H31" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="I31" s="82">
+      <c r="I31" s="73">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="186"/>
-      <c r="C32" s="187"/>
-      <c r="D32" s="188"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
+      <c r="B32" s="167"/>
+      <c r="C32" s="168"/>
+      <c r="D32" s="169"/>
+      <c r="F32" s="67"/>
+      <c r="G32" s="67"/>
       <c r="H32" s="46" t="s">
         <v>16</v>
       </c>
@@ -5125,118 +5064,92 @@
         <f>total_ttc-acompte</f>
         <v>0</v>
       </c>
-      <c r="L32" s="87"/>
-    </row>
-    <row r="34" spans="2:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="53" t="s">
+      <c r="L32" s="78"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="47"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="68"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+    </row>
+    <row r="34" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="156" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="51"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="56"/>
-    </row>
-    <row r="35" spans="2:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="58"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="I35" s="60"/>
+      <c r="C34" s="157"/>
+      <c r="D34" s="158"/>
+      <c r="E34" s="158"/>
+      <c r="F34" s="158"/>
+      <c r="G34" s="158"/>
+      <c r="H34" s="158"/>
+      <c r="I34" s="158"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="47"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="47"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-    </row>
-    <row r="37" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="175" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="176"/>
-      <c r="D37" s="177"/>
-      <c r="E37" s="177"/>
-      <c r="F37" s="177"/>
-      <c r="G37" s="177"/>
-      <c r="H37" s="177"/>
-      <c r="I37" s="177"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="47"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="178" t="str">
+      <c r="B36" s="159" t="str">
         <f>IF(ISBLANK(footer), "", footer)</f>
         <v/>
       </c>
-      <c r="C39" s="178"/>
-      <c r="D39" s="179"/>
-      <c r="E39" s="179"/>
-      <c r="F39" s="179"/>
-      <c r="G39" s="179"/>
-      <c r="H39" s="179"/>
-      <c r="I39" s="179"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="179"/>
-      <c r="C40" s="179"/>
-      <c r="D40" s="179"/>
-      <c r="E40" s="179"/>
-      <c r="F40" s="179"/>
-      <c r="G40" s="179"/>
-      <c r="H40" s="179"/>
-      <c r="I40" s="179"/>
+      <c r="C36" s="159"/>
+      <c r="D36" s="160"/>
+      <c r="E36" s="160"/>
+      <c r="F36" s="160"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="160"/>
+      <c r="I36" s="160"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="160"/>
+      <c r="C37" s="160"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="160"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="160"/>
+      <c r="I37" s="160"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="160"/>
+      <c r="C38" s="160"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="160"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="160"/>
+      <c r="I38" s="160"/>
+    </row>
+    <row r="39" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="74"/>
+      <c r="C39" s="74"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="74"/>
+      <c r="I39" s="74"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="179"/>
-      <c r="C41" s="179"/>
-      <c r="D41" s="179"/>
-      <c r="E41" s="179"/>
-      <c r="F41" s="179"/>
-      <c r="G41" s="179"/>
-      <c r="H41" s="179"/>
-      <c r="I41" s="179"/>
-    </row>
-    <row r="42" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="86"/>
-      <c r="C44" s="86"/>
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" deleteColumns="0" deleteRows="0"/>
   <mergeCells count="5">
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B39:I41"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B36:I38"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D32"/>
@@ -5260,7 +5173,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEFA5FEC-6A62-487A-B625-F70127CA37AE}">
-  <dimension ref="B1:K44"/>
+  <dimension ref="B1:K41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="4" customWidth="1"/>
@@ -5293,7 +5206,7 @@
       <c r="C4" s="7"/>
       <c r="D4" s="8"/>
       <c r="E4" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
@@ -5310,40 +5223,40 @@
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="2:11" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="90" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="89" t="s">
+      <c r="B6" s="81" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="80" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="8"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="171"/>
-      <c r="K6" s="174"/>
+        <v>35</v>
+      </c>
+      <c r="I6" s="152"/>
+      <c r="K6" s="155"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="91" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="89" t="s">
+      <c r="B7" s="82" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="80" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="I7" s="173"/>
+        <v>152</v>
+      </c>
+      <c r="I7" s="154"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="89" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="92" t="s">
+      <c r="B8" s="80" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="83" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="5"/>
@@ -5351,25 +5264,25 @@
       <c r="H8" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="114"/>
+      <c r="I8" s="105"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="89" t="s">
-        <v>42</v>
+      <c r="B9" s="80" t="s">
+        <v>39</v>
       </c>
       <c r="C9" s="43"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="115">
+        <v>41</v>
+      </c>
+      <c r="I9" s="106">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="80" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="42"/>
@@ -5379,7 +5292,7 @@
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="84" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="42"/>
@@ -5391,7 +5304,7 @@
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="89" t="s">
+      <c r="B12" s="80" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="43"/>
@@ -5414,7 +5327,7 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="50" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C14" s="50"/>
       <c r="D14" s="50"/>
@@ -5435,11 +5348,11 @@
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="65" t="str">
+      <c r="B16" s="57" t="str">
         <f>IF(num_client="","Raison sociale",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Raison sociale],""))</f>
         <v>Raison sociale</v>
       </c>
-      <c r="C16" s="65" t="str">
+      <c r="C16" s="57" t="str">
         <f>IF(num_client="","Nom Prénom",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Nom],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Prénom],"")))</f>
         <v>Nom Prénom</v>
       </c>
@@ -5451,11 +5364,11 @@
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="65" t="str">
+      <c r="B17" s="57" t="str">
         <f>IF(num_client="","Nom commercial",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Nom commercial],""))</f>
         <v>Nom commercial</v>
       </c>
-      <c r="C17" s="65" t="str">
+      <c r="C17" s="57" t="str">
         <f>IF(num_client="","Téléphone",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Téléphone],""))</f>
         <v>Téléphone</v>
       </c>
@@ -5467,11 +5380,11 @@
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="65" t="str">
+      <c r="B18" s="57" t="str">
         <f>IF(num_client="","Adresse",_xlfn.CONCAT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation adresse 1],"")," ",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation adresse 2],"")))</f>
         <v>Adresse</v>
       </c>
-      <c r="C18" s="65" t="str">
+      <c r="C18" s="57" t="str">
         <f>IF(num_client="","Email",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Email],""),""))</f>
         <v>Email</v>
       </c>
@@ -5483,11 +5396,11 @@
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="65" t="str">
+      <c r="B19" s="57" t="str">
         <f>IF(num_client="","CP",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation CP],""),""))</f>
         <v>CP</v>
       </c>
-      <c r="C19" s="65" t="str">
+      <c r="C19" s="57" t="str">
         <f>IF(num_client="","TVA",_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[TVA],""))</f>
         <v>TVA</v>
       </c>
@@ -5499,11 +5412,11 @@
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="65" t="str">
+      <c r="B20" s="57" t="str">
         <f>IF(num_client="","Ville",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation Ville],""),""))</f>
         <v>Ville</v>
       </c>
-      <c r="C20" s="65" t="str">
+      <c r="C20" s="57" t="str">
         <f>IF(num_client="","Siret",TEXT(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[SIRET],""),"0"))</f>
         <v>Siret</v>
       </c>
@@ -5515,7 +5428,7 @@
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="65" t="str">
+      <c r="B21" s="57" t="str">
         <f>IF(num_client="","Pays",IFERROR(_xlfn.XLOOKUP(num_client,table_clients[Numéro client],table_clients[Facturation Pays],""),""))</f>
         <v>Pays</v>
       </c>
@@ -5540,11 +5453,11 @@
       <c r="E23" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="F23" s="72" t="s">
+      <c r="F23" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="72" t="s">
-        <v>122</v>
+      <c r="G23" s="64" t="s">
+        <v>119</v>
       </c>
       <c r="H23" s="50" t="s">
         <v>23</v>
@@ -5554,86 +5467,86 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="61"/>
-      <c r="C24" s="61" t="str">
+      <c r="B24" s="53"/>
+      <c r="C24" s="53" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Description],""))</f>
         <v/>
       </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="62" t="str">
+      <c r="D24" s="53"/>
+      <c r="E24" s="54" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F24" s="73" t="str">
+      <c r="F24" s="65" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G24" s="73" t="str">
+      <c r="G24" s="65" t="str">
         <f>IF(B24="","",_xlfn.XLOOKUP(B24,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
-      <c r="H24" s="62"/>
-      <c r="I24" s="88">
+      <c r="H24" s="54"/>
+      <c r="I24" s="79">
         <f>IF(B24="",0,lignes_avoir[[#This Row],[Quantité]]*lignes_avoir[[#This Row],[Prix unitaire HT]]-lignes_avoir[[#This Row],[Remise]])</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="61"/>
-      <c r="C25" s="61" t="str">
+      <c r="B25" s="53"/>
+      <c r="C25" s="53" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Description],""))</f>
         <v/>
       </c>
-      <c r="D25" s="61"/>
-      <c r="E25" s="62" t="str">
+      <c r="D25" s="53"/>
+      <c r="E25" s="54" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F25" s="73" t="str">
+      <c r="F25" s="65" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G25" s="73" t="str">
+      <c r="G25" s="65" t="str">
         <f>IF(B25="","",_xlfn.XLOOKUP(B25,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
-      <c r="H25" s="62"/>
-      <c r="I25" s="88">
+      <c r="H25" s="54"/>
+      <c r="I25" s="79">
         <f>IF(B25="",0,lignes_avoir[[#This Row],[Quantité]]*lignes_avoir[[#This Row],[Prix unitaire HT]]-lignes_avoir[[#This Row],[Remise]])</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="61"/>
-      <c r="C26" s="67" t="str">
+      <c r="B26" s="53"/>
+      <c r="C26" s="59" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Description],""))</f>
         <v/>
       </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68" t="str">
+      <c r="D26" s="59"/>
+      <c r="E26" s="60" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Prix unitaire HT],""))</f>
         <v/>
       </c>
-      <c r="F26" s="74" t="str">
+      <c r="F26" s="66" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Taux TVA],""))</f>
         <v/>
       </c>
-      <c r="G26" s="74" t="str">
+      <c r="G26" s="66" t="str">
         <f>IF(B26="","",_xlfn.XLOOKUP(B26,table_produits[Référence produit],table_produits[Cat],""))</f>
         <v/>
       </c>
-      <c r="H26" s="68"/>
-      <c r="I26" s="88">
+      <c r="H26" s="60"/>
+      <c r="I26" s="79">
         <f>IF(B26="",0,lignes_avoir[[#This Row],[Quantité]]*lignes_avoir[[#This Row],[Prix unitaire HT]]-lignes_avoir[[#This Row],[Remise]])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="180" t="s">
+      <c r="B28" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="181"/>
-      <c r="D28" s="182"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="163"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="16" t="s">
@@ -5645,12 +5558,12 @@
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="183" t="e">
+      <c r="B29" s="164" t="e">
         <f>LEFT(regime_tva,FIND("-",regime_tva)-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="184"/>
-      <c r="D29" s="185"/>
+      <c r="C29" s="165"/>
+      <c r="D29" s="166"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="16" t="s">
@@ -5662,12 +5575,12 @@
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="183" t="str">
+      <c r="B30" s="164" t="str">
         <f>config!PMD&amp;". "&amp;config!PMT&amp;". "&amp;config!AAB&amp;". "</f>
         <v xml:space="preserve">. . . </v>
       </c>
-      <c r="C30" s="184"/>
-      <c r="D30" s="185"/>
+      <c r="C30" s="165"/>
+      <c r="D30" s="166"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="16" t="s">
@@ -5679,22 +5592,22 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="183"/>
-      <c r="C31" s="184"/>
-      <c r="D31" s="185"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="166"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="I31" s="123">
+      <c r="I31" s="114">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="186"/>
-      <c r="C32" s="187"/>
-      <c r="D32" s="188"/>
+      <c r="B32" s="167"/>
+      <c r="C32" s="168"/>
+      <c r="D32" s="169"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="17" t="s">
@@ -5705,115 +5618,89 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="128" t="s">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="24"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="179" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="129"/>
-      <c r="D34" s="130"/>
-      <c r="E34" s="131"/>
-      <c r="F34" s="132"/>
-      <c r="G34" s="132"/>
-      <c r="H34" s="129"/>
-      <c r="I34" s="133"/>
-    </row>
-    <row r="35" spans="2:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="134" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="135"/>
-      <c r="D35" s="130"/>
-      <c r="E35" s="130"/>
-      <c r="F35" s="130"/>
-      <c r="G35" s="130"/>
-      <c r="H35" s="136" t="s">
-        <v>35</v>
-      </c>
-      <c r="I35" s="137"/>
+      <c r="C34" s="180"/>
+      <c r="D34" s="181"/>
+      <c r="E34" s="181"/>
+      <c r="F34" s="181"/>
+      <c r="G34" s="181"/>
+      <c r="H34" s="181"/>
+      <c r="I34" s="181"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="24"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-    </row>
-    <row r="37" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="198" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="199"/>
-      <c r="D37" s="200"/>
-      <c r="E37" s="200"/>
-      <c r="F37" s="200"/>
-      <c r="G37" s="200"/>
-      <c r="H37" s="200"/>
-      <c r="I37" s="200"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="24"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="178" t="str">
+      <c r="B36" s="159" t="str">
         <f>IF(ISBLANK(footer), "", footer)</f>
         <v/>
       </c>
-      <c r="C39" s="178"/>
-      <c r="D39" s="179"/>
-      <c r="E39" s="179"/>
-      <c r="F39" s="179"/>
-      <c r="G39" s="179"/>
-      <c r="H39" s="179"/>
-      <c r="I39" s="179"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="179"/>
-      <c r="C40" s="179"/>
-      <c r="D40" s="179"/>
-      <c r="E40" s="179"/>
-      <c r="F40" s="179"/>
-      <c r="G40" s="179"/>
-      <c r="H40" s="179"/>
-      <c r="I40" s="179"/>
+      <c r="C36" s="159"/>
+      <c r="D36" s="160"/>
+      <c r="E36" s="160"/>
+      <c r="F36" s="160"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="160"/>
+      <c r="I36" s="160"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="160"/>
+      <c r="C37" s="160"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="160"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="160"/>
+      <c r="I37" s="160"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="160"/>
+      <c r="C38" s="160"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="160"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="160"/>
+      <c r="I38" s="160"/>
+    </row>
+    <row r="39" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="179"/>
-      <c r="C41" s="179"/>
-      <c r="D41" s="179"/>
-      <c r="E41" s="179"/>
-      <c r="F41" s="179"/>
-      <c r="G41" s="179"/>
-      <c r="H41" s="179"/>
-      <c r="I41" s="179"/>
-    </row>
-    <row r="42" spans="2:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B39:I41"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B36:I38"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D32"/>
@@ -5862,96 +5749,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="128" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="129" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="130" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="148" t="s">
+      <c r="F1" s="130" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="130" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="149" t="s">
+      <c r="H1" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="149" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="149" t="s">
+      <c r="I1" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="F1" s="149" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="149" t="s">
+      <c r="J1" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="149" t="s">
+      <c r="K1" s="131" t="s">
         <v>134</v>
       </c>
-      <c r="I1" s="149" t="s">
+      <c r="L1" s="130" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="149" t="s">
+      <c r="M1" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="K1" s="150" t="s">
+      <c r="N1" s="130" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="149" t="s">
+      <c r="O1" s="130" t="s">
         <v>138</v>
       </c>
-      <c r="M1" s="149" t="s">
+      <c r="P1" s="131" t="s">
         <v>139</v>
       </c>
-      <c r="N1" s="149" t="s">
+      <c r="Q1" s="130" t="s">
         <v>140</v>
       </c>
-      <c r="O1" s="149" t="s">
+      <c r="R1" s="130" t="s">
         <v>141</v>
       </c>
-      <c r="P1" s="150" t="s">
+      <c r="S1" s="132" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" s="130" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" s="130" t="s">
         <v>142</v>
       </c>
-      <c r="Q1" s="149" t="s">
-        <v>143</v>
-      </c>
-      <c r="R1" s="149" t="s">
-        <v>144</v>
-      </c>
-      <c r="S1" s="151" t="s">
-        <v>4</v>
-      </c>
-      <c r="T1" s="149" t="s">
-        <v>1</v>
-      </c>
-      <c r="U1" s="149" t="s">
-        <v>145</v>
-      </c>
-      <c r="V1" s="152" t="s">
+      <c r="V1" s="133" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="21"/>
       <c r="B2" s="22"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="153"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
-      <c r="K2" s="154"/>
+      <c r="K2" s="135"/>
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="22"/>
       <c r="O2" s="22"/>
-      <c r="P2" s="154"/>
+      <c r="P2" s="135"/>
       <c r="Q2" s="22"/>
       <c r="R2" s="22"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="156"/>
+      <c r="S2" s="136"/>
+      <c r="T2" s="137"/>
       <c r="U2" s="22"/>
-      <c r="V2" s="157"/>
+      <c r="V2" s="138"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5978,7 +5865,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="28" t="s">
         <v>7</v>
@@ -5987,16 +5874,16 @@
         <v>9</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="139" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1" s="139" t="s">
-        <v>124</v>
+        <v>33</v>
+      </c>
+      <c r="F1" s="120" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" s="120" t="s">
+        <v>121</v>
       </c>
       <c r="H1" s="33" t="s">
         <v>25</v>
@@ -6008,8 +5895,8 @@
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
       <c r="E2" s="32"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
       <c r="H2" s="34"/>
     </row>
   </sheetData>
@@ -6032,461 +5919,461 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="55" style="94" customWidth="1"/>
+    <col min="2" max="2" width="55" style="85" customWidth="1"/>
     <col min="3" max="3" width="69.42578125" customWidth="1"/>
-    <col min="4" max="4" width="64.85546875" style="99" customWidth="1"/>
-    <col min="5" max="5" width="54.7109375" style="99" customWidth="1"/>
+    <col min="4" max="4" width="64.85546875" style="90" customWidth="1"/>
+    <col min="5" max="5" width="54.7109375" style="90" customWidth="1"/>
     <col min="6" max="6" width="78.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2" s="99" t="s">
+      <c r="A2" s="85" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="90" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="91" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="92">
+        <v>0.2</v>
+      </c>
+      <c r="C3" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="91" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="89">
+        <v>5.5E-2</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="89">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="C6" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="88">
+        <v>0</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="92">
+        <v>0.2</v>
+      </c>
+      <c r="C8" s="93" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="89">
+        <v>5.5E-2</v>
+      </c>
+      <c r="C10" s="86" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="89">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="C11" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="88">
+        <v>0</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="122" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="92"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="122" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="85" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="88"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="85" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="88"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="88"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="85" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="85" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="88"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="85" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="88"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="85" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="124"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="123" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="85" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="94" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="94" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="94" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="94" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="94" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="94" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="127" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="100" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="101">
-        <v>0.2</v>
-      </c>
-      <c r="C3" s="102" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="100" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="96" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="97">
-        <v>0.1</v>
-      </c>
-      <c r="C4" s="95" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="96" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="98">
-        <v>5.5E-2</v>
-      </c>
-      <c r="C5" s="95" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="96" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6" s="98">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="C6" s="95" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="96" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="97">
-        <v>0</v>
-      </c>
-      <c r="C7" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="100" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="101">
-        <v>0.2</v>
-      </c>
-      <c r="C8" s="102" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="100" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="100" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="96" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="97">
-        <v>0.1</v>
-      </c>
-      <c r="C9" s="95" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="96" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="98">
-        <v>5.5E-2</v>
-      </c>
-      <c r="C10" s="95" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="96" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="98">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="C11" s="95" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="96" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="97">
-        <v>0</v>
-      </c>
-      <c r="C12" s="95" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="141" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="101"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="141" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="94" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="97"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="94" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="94" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="97"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="94" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="94" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="97"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="94" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="94" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="97"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="94" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="97"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="94" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="142" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="143"/>
-      <c r="C19" s="144"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="142" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="96"/>
-      <c r="B20" s="96"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="94" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="103" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="103" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="103" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="103" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="103" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="103" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="103" t="s">
-        <v>104</v>
-      </c>
-      <c r="B29" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="103" t="s">
+      <c r="C31" t="s">
         <v>106</v>
       </c>
-      <c r="B30" t="s">
+    </row>
+    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="C30" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="103" t="s">
+      <c r="B32" s="127" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="94" t="s">
         <v>108</v>
-      </c>
-      <c r="B31" s="146" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="103" t="s">
-        <v>110</v>
-      </c>
-      <c r="B32" s="146" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="103" t="s">
-        <v>111</v>
       </c>
       <c r="B33"/>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="94" t="s">
-        <v>64</v>
+      <c r="A36" s="85" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" s="94" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="B37" s="85" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" s="94" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="B38" s="85" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="94" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+      <c r="B39" s="85" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="94" t="s">
-        <v>55</v>
+        <v>51</v>
+      </c>
+      <c r="B40" s="85" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="94" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="B41" s="85" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>58</v>
-      </c>
-      <c r="B42" s="94" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+      <c r="B42" s="85" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" s="94" t="s">
-        <v>61</v>
+        <v>57</v>
+      </c>
+      <c r="B43" s="85" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" s="94" t="s">
-        <v>63</v>
+        <v>59</v>
+      </c>
+      <c r="B44" s="85" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6509,130 +6396,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="159" t="s">
-        <v>147</v>
+      <c r="B1" s="140" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="138"/>
+        <v>36</v>
+      </c>
+      <c r="B2" s="119"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="138"/>
+        <v>37</v>
+      </c>
+      <c r="B3" s="119"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="158"/>
+        <v>40</v>
+      </c>
+      <c r="B4" s="139"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="138"/>
+      <c r="B5" s="119"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="138"/>
+        <v>38</v>
+      </c>
+      <c r="B6" s="119"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="138"/>
+        <v>39</v>
+      </c>
+      <c r="B7" s="119"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="138"/>
+      <c r="B8" s="119"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="138"/>
+      <c r="B9" s="119"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="138"/>
+      <c r="B10" s="119"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="138"/>
+      <c r="B11" s="119"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="138"/>
+      <c r="B12" s="119"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="138"/>
+      <c r="B13" s="119"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="160"/>
+        <v>145</v>
+      </c>
+      <c r="B14" s="141"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="120" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" s="161"/>
-      <c r="E15" s="162"/>
-      <c r="F15" s="162"/>
+      <c r="A15" s="111" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="142"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="143"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>149</v>
-      </c>
-      <c r="D16" s="162"/>
-      <c r="E16" s="162"/>
-      <c r="F16" s="163"/>
+        <v>146</v>
+      </c>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="144"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>150</v>
-      </c>
-      <c r="D17" s="162"/>
-      <c r="E17" s="162"/>
-      <c r="F17" s="163"/>
+        <v>147</v>
+      </c>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="144"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -6651,48 +6538,48 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="94.140625" style="106" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="107" customWidth="1"/>
+    <col min="2" max="2" width="94.140625" style="97" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="98" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" customWidth="1"/>
     <col min="5" max="5" width="5.140625" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="85" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="97" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="85" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" s="97" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="94" t="s">
+    <row r="6" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="97" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="99"/>
+      <c r="E6" s="99"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="85" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" s="97" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="106" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="106" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="108"/>
-      <c r="E6" s="108"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="94" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B9" s="106" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
